--- a/website/Website Rates (for Google Sheet).xlsx
+++ b/website/Website Rates (for Google Sheet).xlsx
@@ -448,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H146"/>
+  <dimension ref="A1:H140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -721,7 +721,6 @@
           <t>T-100</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
           <t>Clutchers</t>
@@ -733,7 +732,6 @@
       <c r="E8" t="n">
         <v>1</v>
       </c>
-      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -751,7 +749,6 @@
           <t>TESLA-701</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
           <t>Clutchers</t>
@@ -781,14 +778,13 @@
           <t>TESLA-702</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
           <t>Clutchers</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>60</v>
+        <v>108</v>
       </c>
       <c r="E10" t="n">
         <v>6</v>
@@ -803,7 +799,11 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr"/>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>Rate 24 Oct 2026: ₹60 → ₹108.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -811,7 +811,6 @@
           <t>TESLA-703</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
           <t>Clutchers</t>
@@ -841,7 +840,6 @@
           <t>TESLA-707</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
           <t>Clutchers</t>
@@ -871,7 +869,6 @@
           <t>TESLA-710</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
           <t>Clutchers</t>
@@ -901,7 +898,6 @@
           <t>TESLA-711</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
           <t>Clutchers</t>
@@ -931,7 +927,6 @@
           <t>TESLA-712</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr">
         <is>
           <t>Clutchers</t>
@@ -961,7 +956,6 @@
           <t>TESLA-713</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr">
         <is>
           <t>Clutchers</t>
@@ -991,7 +985,6 @@
           <t>TESLA-714</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
           <t>Clutchers</t>
@@ -1055,7 +1048,6 @@
           <t>TESLA-716</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
           <t>Clutchers</t>
@@ -1085,7 +1077,6 @@
           <t>TESLA-717</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr">
         <is>
           <t>Clutchers</t>
@@ -1115,7 +1106,6 @@
           <t>TESLA-718</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr">
         <is>
           <t>Clutchers</t>
@@ -1145,7 +1135,6 @@
           <t>TESLA-719</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr">
         <is>
           <t>Clutchers</t>
@@ -1220,12 +1209,11 @@
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="E24" t="n">
         <v>4</v>
       </c>
-      <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
           <t>Y</t>
@@ -1233,7 +1221,7 @@
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>No catalogue photo yet.</t>
+          <t>No catalogue photo yet. Rate 24 Oct 2026: ₹81 → ₹78.</t>
         </is>
       </c>
     </row>
@@ -1243,7 +1231,6 @@
           <t>TESLA-722</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr">
         <is>
           <t>Clutchers</t>
@@ -1273,7 +1260,6 @@
           <t>TESLA-751</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr">
         <is>
           <t>Clutchers</t>
@@ -1303,7 +1289,6 @@
           <t>TESLA-752</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr">
         <is>
           <t>Clutchers</t>
@@ -1333,7 +1318,6 @@
           <t>TESLA-753</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr"/>
       <c r="C28" t="inlineStr">
         <is>
           <t>Clutchers</t>
@@ -1401,7 +1385,6 @@
           <t>100 PC NYLON RUBBER</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr">
         <is>
           <t>Scrunchies</t>
@@ -1413,7 +1396,6 @@
       <c r="E30" t="n">
         <v>1</v>
       </c>
-      <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
           <t>Y</t>
@@ -1438,7 +1420,7 @@
         </is>
       </c>
       <c r="D31" s="5" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E31" s="4" t="n">
         <v>1</v>
@@ -1455,7 +1437,7 @@
       </c>
       <c r="H31" s="6" t="inlineStr">
         <is>
-          <t>Not the same as RC-300 fur chimta (clutchers, ₹90).</t>
+          <t>Not the same as RC-300 fur chimta (clutchers, ₹90). Rate 24 Oct 2026: ₹57 → ₹60.</t>
         </is>
       </c>
     </row>
@@ -1465,7 +1447,6 @@
           <t>322</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr"/>
       <c r="C32" t="inlineStr">
         <is>
           <t>Scrunchies</t>
@@ -1495,14 +1476,13 @@
           <t>335</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr"/>
       <c r="C33" t="inlineStr">
         <is>
           <t>Scrunchies</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>36</v>
+        <v>37.5</v>
       </c>
       <c r="E33" t="n">
         <v>6</v>
@@ -1517,7 +1497,11 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="H33" s="3" t="inlineStr"/>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>Rate 24 Oct 2026: ₹36 → ₹37.5.</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1525,7 +1509,6 @@
           <t>349</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr"/>
       <c r="C34" t="inlineStr">
         <is>
           <t>Scrunchies</t>
@@ -1555,7 +1538,6 @@
           <t>355</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr"/>
       <c r="C35" t="inlineStr">
         <is>
           <t>Scrunchies</t>
@@ -1585,7 +1567,6 @@
           <t>36 PC NYLON RUBBER</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr"/>
       <c r="C36" t="inlineStr">
         <is>
           <t>Scrunchies</t>
@@ -1622,7 +1603,7 @@
         </is>
       </c>
       <c r="D37" s="5" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="E37" s="4" t="n">
         <v>8</v>
@@ -1639,7 +1620,7 @@
       </c>
       <c r="H37" s="6" t="inlineStr">
         <is>
-          <t>Not the same as RC-400 fur chimta (clutchers, ₹150).</t>
+          <t>Not the same as RC-400 fur chimta (clutchers, ₹150). Rate 24 Oct 2026: ₹63 → ₹66.</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1630,6 @@
           <t>430</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr">
         <is>
           <t>Scrunchies</t>
@@ -1661,7 +1641,6 @@
       <c r="E38" t="n">
         <v>4</v>
       </c>
-      <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
           <t>Y</t>
@@ -1679,7 +1658,6 @@
           <t>432</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr"/>
       <c r="C39" t="inlineStr">
         <is>
           <t>Scrunchies</t>
@@ -1709,7 +1687,6 @@
           <t>433</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr"/>
       <c r="C40" t="inlineStr">
         <is>
           <t>Scrunchies</t>
@@ -1739,7 +1716,6 @@
           <t>434</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr"/>
       <c r="C41" t="inlineStr">
         <is>
           <t>Scrunchies</t>
@@ -1769,7 +1745,6 @@
           <t>437</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr"/>
       <c r="C42" t="inlineStr">
         <is>
           <t>Scrunchies</t>
@@ -1781,7 +1756,6 @@
       <c r="E42" t="n">
         <v>4</v>
       </c>
-      <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
           <t>Y</t>
@@ -1799,7 +1773,6 @@
           <t>438</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr"/>
       <c r="C43" t="inlineStr">
         <is>
           <t>Scrunchies</t>
@@ -1859,7 +1832,6 @@
           <t>903</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr">
         <is>
           <t>Scrunchies</t>
@@ -1889,7 +1861,6 @@
           <t>912</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr"/>
       <c r="C46" t="inlineStr">
         <is>
           <t>Scrunchies</t>
@@ -1901,7 +1872,6 @@
       <c r="E46" t="n">
         <v>5</v>
       </c>
-      <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
           <t>Y</t>
@@ -1919,7 +1889,6 @@
           <t>913</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr"/>
       <c r="C47" t="inlineStr">
         <is>
           <t>Scrunchies</t>
@@ -1931,7 +1900,6 @@
       <c r="E47" t="n">
         <v>5</v>
       </c>
-      <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
           <t>Y</t>
@@ -1949,7 +1917,6 @@
           <t>914</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr"/>
       <c r="C48" t="inlineStr">
         <is>
           <t>Scrunchies</t>
@@ -1961,7 +1928,6 @@
       <c r="E48" t="n">
         <v>6</v>
       </c>
-      <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
           <t>Y</t>
@@ -1979,7 +1945,6 @@
           <t>917</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr"/>
       <c r="C49" t="inlineStr">
         <is>
           <t>Scrunchies</t>
@@ -1991,7 +1956,6 @@
       <c r="E49" t="n">
         <v>5</v>
       </c>
-      <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
           <t>Y</t>
@@ -2009,7 +1973,6 @@
           <t>920</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr"/>
       <c r="C50" t="inlineStr">
         <is>
           <t>Scrunchies</t>
@@ -2039,7 +2002,6 @@
           <t>931</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr"/>
       <c r="C51" t="inlineStr">
         <is>
           <t>Scrunchies</t>
@@ -2069,7 +2031,6 @@
           <t>933</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr"/>
       <c r="C52" t="inlineStr">
         <is>
           <t>Scrunchies</t>
@@ -2081,7 +2042,6 @@
       <c r="E52" t="n">
         <v>6</v>
       </c>
-      <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
           <t>Y</t>
@@ -2099,7 +2059,6 @@
           <t>934</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr"/>
       <c r="C53" t="inlineStr">
         <is>
           <t>Scrunchies</t>
@@ -2129,7 +2088,6 @@
           <t>940</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr"/>
       <c r="C54" t="inlineStr">
         <is>
           <t>Scrunchies</t>
@@ -2159,7 +2117,6 @@
           <t>941</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr"/>
       <c r="C55" t="inlineStr">
         <is>
           <t>Scrunchies</t>
@@ -2171,7 +2128,6 @@
       <c r="E55" t="n">
         <v>5</v>
       </c>
-      <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
           <t>Y</t>
@@ -2189,7 +2145,6 @@
           <t>945</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr"/>
       <c r="C56" t="inlineStr">
         <is>
           <t>Scrunchies</t>
@@ -2201,7 +2156,6 @@
       <c r="E56" t="n">
         <v>6</v>
       </c>
-      <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
           <t>Y</t>
@@ -2219,7 +2173,6 @@
           <t>952</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr"/>
       <c r="C57" t="inlineStr">
         <is>
           <t>Scrunchies</t>
@@ -2249,7 +2202,6 @@
           <t>960</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr"/>
       <c r="C58" t="inlineStr">
         <is>
           <t>Scrunchies</t>
@@ -2279,14 +2231,13 @@
           <t>965</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr"/>
       <c r="C59" t="inlineStr">
         <is>
           <t>Scrunchies</t>
         </is>
       </c>
       <c r="D59" s="2" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E59" t="n">
         <v>10</v>
@@ -2301,7 +2252,11 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="H59" s="3" t="inlineStr"/>
+      <c r="H59" s="3" t="inlineStr">
+        <is>
+          <t>Rate 24 Oct 2026: ₹39 → ₹42.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2309,7 +2264,6 @@
           <t>967</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr"/>
       <c r="C60" t="inlineStr">
         <is>
           <t>Scrunchies</t>
@@ -2339,7 +2293,6 @@
           <t>980</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr"/>
       <c r="C61" t="inlineStr">
         <is>
           <t>Scrunchies</t>
@@ -2369,7 +2322,6 @@
           <t>986</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr"/>
       <c r="C62" t="inlineStr">
         <is>
           <t>Scrunchies</t>
@@ -2399,7 +2351,6 @@
           <t>991</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr"/>
       <c r="C63" t="inlineStr">
         <is>
           <t>Scrunchies</t>
@@ -2429,14 +2380,13 @@
           <t>993</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr"/>
       <c r="C64" t="inlineStr">
         <is>
           <t>Scrunchies</t>
         </is>
       </c>
       <c r="D64" s="2" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E64" t="n">
         <v>5</v>
@@ -2451,7 +2401,11 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="H64" s="3" t="inlineStr"/>
+      <c r="H64" s="3" t="inlineStr">
+        <is>
+          <t>Rate 24 Oct 2026: ₹57 → ₹60.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2459,14 +2413,13 @@
           <t>996</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr"/>
       <c r="C65" t="inlineStr">
         <is>
           <t>Scrunchies</t>
         </is>
       </c>
       <c r="D65" s="2" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="E65" t="n">
         <v>5</v>
@@ -2481,7 +2434,11 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="H65" s="3" t="inlineStr"/>
+      <c r="H65" s="3" t="inlineStr">
+        <is>
+          <t>Rate 24 Oct 2026: ₹54 → ₹57.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2489,14 +2446,13 @@
           <t>998</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr"/>
       <c r="C66" t="inlineStr">
         <is>
           <t>Scrunchies</t>
         </is>
       </c>
       <c r="D66" s="2" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="E66" t="n">
         <v>5</v>
@@ -2511,7 +2467,11 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="H66" s="3" t="inlineStr"/>
+      <c r="H66" s="3" t="inlineStr">
+        <is>
+          <t>Rate 24 Oct 2026: ₹60 → ₹63.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2519,14 +2479,13 @@
           <t>BS-01</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr"/>
       <c r="C67" t="inlineStr">
         <is>
           <t>Scrunchies</t>
         </is>
       </c>
       <c r="D67" s="2" t="n">
-        <v>58.5</v>
+        <v>57</v>
       </c>
       <c r="E67" t="n">
         <v>6</v>
@@ -2541,7 +2500,11 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="H67" s="3" t="inlineStr"/>
+      <c r="H67" s="3" t="inlineStr">
+        <is>
+          <t>Rate 24 Oct 2026: ₹58.5 → ₹57.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2549,7 +2512,6 @@
           <t>BS-02</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr"/>
       <c r="C68" t="inlineStr">
         <is>
           <t>Scrunchies</t>
@@ -2579,14 +2541,13 @@
           <t>BS-03</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr"/>
       <c r="C69" t="inlineStr">
         <is>
           <t>Scrunchies</t>
         </is>
       </c>
       <c r="D69" s="2" t="n">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="E69" t="n">
         <v>3</v>
@@ -2601,7 +2562,11 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="H69" s="3" t="inlineStr"/>
+      <c r="H69" s="3" t="inlineStr">
+        <is>
+          <t>Rate 24 Oct 2026: ₹114 → ₹105.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2609,19 +2574,17 @@
           <t>D-01</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr"/>
       <c r="C70" t="inlineStr">
         <is>
           <t>Scrunchies</t>
         </is>
       </c>
       <c r="D70" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E70" t="n">
         <v>12</v>
       </c>
-      <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
           <t>Y</t>
@@ -2629,7 +2592,7 @@
       </c>
       <c r="H70" s="3" t="inlineStr">
         <is>
-          <t>No catalogue photo yet.</t>
+          <t>No catalogue photo yet. Rate 24 Oct 2026: ₹16 → ₹17.</t>
         </is>
       </c>
     </row>
@@ -2639,14 +2602,13 @@
           <t>D-02</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr"/>
       <c r="C71" t="inlineStr">
         <is>
           <t>Scrunchies</t>
         </is>
       </c>
       <c r="D71" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E71" t="n">
         <v>12</v>
@@ -2661,7 +2623,11 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="H71" s="3" t="inlineStr"/>
+      <c r="H71" s="3" t="inlineStr">
+        <is>
+          <t>Rate 24 Oct 2026: ₹16 → ₹17.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2669,7 +2635,6 @@
           <t>D-03</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr"/>
       <c r="C72" t="inlineStr">
         <is>
           <t>Scrunchies</t>
@@ -2699,14 +2664,13 @@
           <t>D-04</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr"/>
       <c r="C73" t="inlineStr">
         <is>
           <t>Scrunchies</t>
         </is>
       </c>
       <c r="D73" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E73" t="n">
         <v>12</v>
@@ -2721,7 +2685,11 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="H73" s="3" t="inlineStr"/>
+      <c r="H73" s="3" t="inlineStr">
+        <is>
+          <t>Rate 24 Oct 2026: ₹16 → ₹17.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2729,7 +2697,6 @@
           <t>D-05</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr"/>
       <c r="C74" t="inlineStr">
         <is>
           <t>Scrunchies</t>
@@ -2759,14 +2726,13 @@
           <t>D-06</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr"/>
       <c r="C75" t="inlineStr">
         <is>
           <t>Scrunchies</t>
         </is>
       </c>
       <c r="D75" s="2" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="E75" t="n">
         <v>12</v>
@@ -2781,7 +2747,11 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="H75" s="3" t="inlineStr"/>
+      <c r="H75" s="3" t="inlineStr">
+        <is>
+          <t>Rate 24 Oct 2026: ₹13.5 → ₹14.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2789,7 +2759,6 @@
           <t>D-07</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr"/>
       <c r="C76" t="inlineStr">
         <is>
           <t>Scrunchies</t>
@@ -2819,14 +2788,13 @@
           <t>D-08</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr"/>
       <c r="C77" t="inlineStr">
         <is>
           <t>Scrunchies</t>
         </is>
       </c>
       <c r="D77" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E77" t="n">
         <v>12</v>
@@ -2841,7 +2809,11 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="H77" s="3" t="inlineStr"/>
+      <c r="H77" s="3" t="inlineStr">
+        <is>
+          <t>Rate 24 Oct 2026: ₹12 → ₹13.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2849,7 +2821,6 @@
           <t>D-09</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr"/>
       <c r="C78" t="inlineStr">
         <is>
           <t>Scrunchies</t>
@@ -2861,7 +2832,6 @@
       <c r="E78" t="n">
         <v>12</v>
       </c>
-      <c r="F78" t="inlineStr"/>
       <c r="G78" t="inlineStr">
         <is>
           <t>Y</t>
@@ -2879,14 +2849,13 @@
           <t>D-10</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr"/>
       <c r="C79" t="inlineStr">
         <is>
           <t>Scrunchies</t>
         </is>
       </c>
       <c r="D79" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E79" t="n">
         <v>12</v>
@@ -2901,7 +2870,11 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="H79" s="3" t="inlineStr"/>
+      <c r="H79" s="3" t="inlineStr">
+        <is>
+          <t>Rate 24 Oct 2026: ₹16 → ₹17.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="4" t="inlineStr">
@@ -3011,7 +2984,6 @@
           <t>MOBILON CARD</t>
         </is>
       </c>
-      <c r="B83" t="inlineStr"/>
       <c r="C83" t="inlineStr">
         <is>
           <t>Scrunchies</t>
@@ -3023,7 +2995,6 @@
       <c r="E83" t="n">
         <v>12</v>
       </c>
-      <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr">
         <is>
           <t>Y</t>
@@ -3041,7 +3012,6 @@
           <t>PS-01</t>
         </is>
       </c>
-      <c r="B84" t="inlineStr"/>
       <c r="C84" t="inlineStr">
         <is>
           <t>Scrunchies</t>
@@ -3053,7 +3023,6 @@
       <c r="E84" t="n">
         <v>6</v>
       </c>
-      <c r="F84" t="inlineStr"/>
       <c r="G84" t="inlineStr">
         <is>
           <t>Y</t>
@@ -3105,7 +3074,6 @@
           <t>RC-202</t>
         </is>
       </c>
-      <c r="B86" t="inlineStr"/>
       <c r="C86" t="inlineStr">
         <is>
           <t>Scrunchies</t>
@@ -3135,7 +3103,6 @@
           <t>RC-254</t>
         </is>
       </c>
-      <c r="B87" t="inlineStr"/>
       <c r="C87" t="inlineStr">
         <is>
           <t>Scrunchies</t>
@@ -3147,7 +3114,6 @@
       <c r="E87" t="n">
         <v>3</v>
       </c>
-      <c r="F87" t="inlineStr"/>
       <c r="G87" t="inlineStr">
         <is>
           <t>Y</t>
@@ -3176,7 +3142,7 @@
         </is>
       </c>
       <c r="D88" s="2" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E88" t="n">
         <v>6</v>
@@ -3191,7 +3157,11 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="H88" s="3" t="inlineStr"/>
+      <c r="H88" s="3" t="inlineStr">
+        <is>
+          <t>Rate 24 Oct 2026: ₹81 → ₹84.</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -3215,7 +3185,6 @@
       <c r="E89" t="n">
         <v>10</v>
       </c>
-      <c r="F89" t="inlineStr"/>
       <c r="G89" t="inlineStr">
         <is>
           <t>Y</t>
@@ -3233,7 +3202,6 @@
           <t>RC-611</t>
         </is>
       </c>
-      <c r="B90" t="inlineStr"/>
       <c r="C90" t="inlineStr">
         <is>
           <t>Scrunchies</t>
@@ -3245,7 +3213,6 @@
       <c r="E90" t="n">
         <v>6</v>
       </c>
-      <c r="F90" t="inlineStr"/>
       <c r="G90" t="inlineStr">
         <is>
           <t>Y</t>
@@ -3263,7 +3230,6 @@
           <t>RC-612</t>
         </is>
       </c>
-      <c r="B91" t="inlineStr"/>
       <c r="C91" t="inlineStr">
         <is>
           <t>Scrunchies</t>
@@ -3275,7 +3241,6 @@
       <c r="E91" t="n">
         <v>6</v>
       </c>
-      <c r="F91" t="inlineStr"/>
       <c r="G91" t="inlineStr">
         <is>
           <t>Y</t>
@@ -3304,7 +3269,7 @@
         </is>
       </c>
       <c r="D92" s="5" t="n">
-        <v>30</v>
+        <v>31.5</v>
       </c>
       <c r="E92" s="4" t="n">
         <v>10</v>
@@ -3321,7 +3286,7 @@
       </c>
       <c r="H92" s="6" t="inlineStr">
         <is>
-          <t>Catalogue says T-613 – same item?</t>
+          <t>Catalogue says T-613 – same item? Rate 24 Oct 2026: ₹30 → ₹31.5.</t>
         </is>
       </c>
     </row>
@@ -3338,7 +3303,7 @@
         </is>
       </c>
       <c r="D93" s="5" t="n">
-        <v>30</v>
+        <v>31.5</v>
       </c>
       <c r="E93" s="4" t="n">
         <v>10</v>
@@ -3355,7 +3320,7 @@
       </c>
       <c r="H93" s="6" t="inlineStr">
         <is>
-          <t>Catalogue says T-614 – same item?</t>
+          <t>Catalogue says T-614 – same item? Rate 24 Oct 2026: ₹30 → ₹31.5.</t>
         </is>
       </c>
     </row>
@@ -3365,19 +3330,17 @@
           <t>RC-615</t>
         </is>
       </c>
-      <c r="B94" t="inlineStr"/>
       <c r="C94" t="inlineStr">
         <is>
           <t>Scrunchies</t>
         </is>
       </c>
       <c r="D94" s="2" t="n">
-        <v>30</v>
+        <v>31.5</v>
       </c>
       <c r="E94" t="n">
         <v>10</v>
       </c>
-      <c r="F94" t="inlineStr"/>
       <c r="G94" t="inlineStr">
         <is>
           <t>Y</t>
@@ -3385,7 +3348,7 @@
       </c>
       <c r="H94" s="3" t="inlineStr">
         <is>
-          <t>No catalogue photo yet.</t>
+          <t>No catalogue photo yet. Rate 24 Oct 2026: ₹30 → ₹31.5.</t>
         </is>
       </c>
     </row>
@@ -3395,7 +3358,6 @@
           <t>RC-616</t>
         </is>
       </c>
-      <c r="B95" t="inlineStr"/>
       <c r="C95" t="inlineStr">
         <is>
           <t>Scrunchies</t>
@@ -3407,7 +3369,6 @@
       <c r="E95" t="n">
         <v>10</v>
       </c>
-      <c r="F95" t="inlineStr"/>
       <c r="G95" t="inlineStr">
         <is>
           <t>Y</t>
@@ -3425,7 +3386,6 @@
           <t>RC-617</t>
         </is>
       </c>
-      <c r="B96" t="inlineStr"/>
       <c r="C96" t="inlineStr">
         <is>
           <t>Scrunchies</t>
@@ -3523,14 +3483,13 @@
           <t>RJ-1001</t>
         </is>
       </c>
-      <c r="B99" t="inlineStr"/>
       <c r="C99" t="inlineStr">
         <is>
           <t>Scrunchies</t>
         </is>
       </c>
       <c r="D99" s="2" t="n">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="E99" t="n">
         <v>5</v>
@@ -3545,7 +3504,11 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="H99" s="3" t="inlineStr"/>
+      <c r="H99" s="3" t="inlineStr">
+        <is>
+          <t>Rate 24 Oct 2026: ₹90 → ₹96.</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -3553,14 +3516,13 @@
           <t>RJ-1002</t>
         </is>
       </c>
-      <c r="B100" t="inlineStr"/>
       <c r="C100" t="inlineStr">
         <is>
           <t>Scrunchies</t>
         </is>
       </c>
       <c r="D100" s="2" t="n">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="E100" t="n">
         <v>6</v>
@@ -3575,7 +3537,11 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="H100" s="3" t="inlineStr"/>
+      <c r="H100" s="3" t="inlineStr">
+        <is>
+          <t>Rate 24 Oct 2026: ₹90 → ₹102.</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -3583,14 +3549,13 @@
           <t>RJ-1003</t>
         </is>
       </c>
-      <c r="B101" t="inlineStr"/>
       <c r="C101" t="inlineStr">
         <is>
           <t>Scrunchies</t>
         </is>
       </c>
       <c r="D101" s="2" t="n">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="E101" t="n">
         <v>6</v>
@@ -3605,7 +3570,11 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="H101" s="3" t="inlineStr"/>
+      <c r="H101" s="3" t="inlineStr">
+        <is>
+          <t>Rate 24 Oct 2026: ₹96 → ₹108.</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -3613,14 +3582,13 @@
           <t>RJ-1004</t>
         </is>
       </c>
-      <c r="B102" t="inlineStr"/>
       <c r="C102" t="inlineStr">
         <is>
           <t>Scrunchies</t>
         </is>
       </c>
       <c r="D102" s="2" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E102" t="n">
         <v>6</v>
@@ -3635,7 +3603,11 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="H102" s="3" t="inlineStr"/>
+      <c r="H102" s="3" t="inlineStr">
+        <is>
+          <t>Rate 24 Oct 2026: ₹51 → ₹54.</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -3643,19 +3615,17 @@
           <t>RJ-1005</t>
         </is>
       </c>
-      <c r="B103" t="inlineStr"/>
       <c r="C103" t="inlineStr">
         <is>
           <t>Scrunchies</t>
         </is>
       </c>
       <c r="D103" s="2" t="n">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="E103" t="n">
         <v>6</v>
       </c>
-      <c r="F103" t="inlineStr"/>
       <c r="G103" t="inlineStr">
         <is>
           <t>Y</t>
@@ -3663,7 +3633,7 @@
       </c>
       <c r="H103" s="3" t="inlineStr">
         <is>
-          <t>No catalogue photo yet.</t>
+          <t>No catalogue photo yet. Rate 24 Oct 2026: ₹108 → ₹120.</t>
         </is>
       </c>
     </row>
@@ -3673,19 +3643,17 @@
           <t>RJ-1006</t>
         </is>
       </c>
-      <c r="B104" t="inlineStr"/>
       <c r="C104" t="inlineStr">
         <is>
           <t>Scrunchies</t>
         </is>
       </c>
       <c r="D104" s="2" t="n">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="E104" t="n">
         <v>6</v>
       </c>
-      <c r="F104" t="inlineStr"/>
       <c r="G104" t="inlineStr">
         <is>
           <t>Y</t>
@@ -3693,7 +3661,7 @@
       </c>
       <c r="H104" s="3" t="inlineStr">
         <is>
-          <t>No catalogue photo yet.</t>
+          <t>No catalogue photo yet. Rate 24 Oct 2026: ₹72 → ₹78.</t>
         </is>
       </c>
     </row>
@@ -3703,19 +3671,17 @@
           <t>RJ-1007</t>
         </is>
       </c>
-      <c r="B105" t="inlineStr"/>
       <c r="C105" t="inlineStr">
         <is>
           <t>Scrunchies</t>
         </is>
       </c>
       <c r="D105" s="2" t="n">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="E105" t="n">
         <v>3</v>
       </c>
-      <c r="F105" t="inlineStr"/>
       <c r="G105" t="inlineStr">
         <is>
           <t>Y</t>
@@ -3723,7 +3689,7 @@
       </c>
       <c r="H105" s="3" t="inlineStr">
         <is>
-          <t>No catalogue photo yet.</t>
+          <t>No catalogue photo yet. Rate 24 Oct 2026: ₹102 → ₹108.</t>
         </is>
       </c>
     </row>
@@ -3744,7 +3710,7 @@
         </is>
       </c>
       <c r="D106" s="2" t="n">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="E106" t="n">
         <v>10</v>
@@ -3759,7 +3725,11 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="H106" s="3" t="inlineStr"/>
+      <c r="H106" s="3" t="inlineStr">
+        <is>
+          <t>Rate 24 Oct 2026: ₹81 → ₹78.</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -3812,7 +3782,7 @@
         </is>
       </c>
       <c r="D108" s="2" t="n">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="E108" t="n">
         <v>10</v>
@@ -3827,7 +3797,11 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="H108" s="3" t="inlineStr"/>
+      <c r="H108" s="3" t="inlineStr">
+        <is>
+          <t>Rate 24 Oct 2026: ₹90 → ₹87.</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -3846,7 +3820,7 @@
         </is>
       </c>
       <c r="D109" s="2" t="n">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="E109" t="n">
         <v>10</v>
@@ -3861,7 +3835,11 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="H109" s="3" t="inlineStr"/>
+      <c r="H109" s="3" t="inlineStr">
+        <is>
+          <t>Rate 24 Oct 2026: ₹108 → ₹105.</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -3880,7 +3858,7 @@
         </is>
       </c>
       <c r="D110" s="2" t="n">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="E110" t="n">
         <v>10</v>
@@ -3895,7 +3873,11 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="H110" s="3" t="inlineStr"/>
+      <c r="H110" s="3" t="inlineStr">
+        <is>
+          <t>Rate 24 Oct 2026: ₹126 → ₹120.</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -3914,7 +3896,7 @@
         </is>
       </c>
       <c r="D111" s="2" t="n">
-        <v>150</v>
+        <v>138</v>
       </c>
       <c r="E111" t="n">
         <v>10</v>
@@ -3929,7 +3911,11 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="H111" s="3" t="inlineStr"/>
+      <c r="H111" s="3" t="inlineStr">
+        <is>
+          <t>Rate 24 Oct 2026: ₹150 → ₹138.</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -3948,7 +3934,7 @@
         </is>
       </c>
       <c r="D112" s="2" t="n">
-        <v>180</v>
+        <v>156</v>
       </c>
       <c r="E112" t="n">
         <v>10</v>
@@ -3963,7 +3949,11 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="H112" s="3" t="inlineStr"/>
+      <c r="H112" s="3" t="inlineStr">
+        <is>
+          <t>Rate 24 Oct 2026: ₹180 → ₹156.</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="4" t="inlineStr">
@@ -4025,7 +4015,6 @@
       <c r="E114" t="n">
         <v>6</v>
       </c>
-      <c r="F114" t="inlineStr"/>
       <c r="G114" t="inlineStr">
         <is>
           <t>Y</t>
@@ -4054,7 +4043,7 @@
         </is>
       </c>
       <c r="D115" s="2" t="n">
-        <v>198</v>
+        <v>180</v>
       </c>
       <c r="E115" t="n">
         <v>10</v>
@@ -4069,7 +4058,11 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="H115" s="3" t="inlineStr"/>
+      <c r="H115" s="3" t="inlineStr">
+        <is>
+          <t>Rate 24 Oct 2026: ₹198 → ₹180.</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -4088,7 +4081,7 @@
         </is>
       </c>
       <c r="D116" s="2" t="n">
-        <v>220</v>
+        <v>204</v>
       </c>
       <c r="E116" t="n">
         <v>10</v>
@@ -4103,7 +4096,11 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="H116" s="3" t="inlineStr"/>
+      <c r="H116" s="3" t="inlineStr">
+        <is>
+          <t>Rate 24 Oct 2026: ₹220 → ₹204.</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -4111,7 +4108,6 @@
           <t>SUMO-RINKLE</t>
         </is>
       </c>
-      <c r="B117" t="inlineStr"/>
       <c r="C117" t="inlineStr">
         <is>
           <t>Scrunchies</t>
@@ -4141,7 +4137,6 @@
           <t>TIER RUBED</t>
         </is>
       </c>
-      <c r="B118" t="inlineStr"/>
       <c r="C118" t="inlineStr">
         <is>
           <t>Scrunchies</t>
@@ -4153,7 +4148,6 @@
       <c r="E118" t="n">
         <v>10</v>
       </c>
-      <c r="F118" t="inlineStr"/>
       <c r="G118" t="inlineStr">
         <is>
           <t>Y</t>
@@ -4171,7 +4165,6 @@
           <t>XL 30 PC</t>
         </is>
       </c>
-      <c r="B119" t="inlineStr"/>
       <c r="C119" t="inlineStr">
         <is>
           <t>Scrunchies</t>
@@ -4231,7 +4224,6 @@
           <t>XL 72 PC RUBED</t>
         </is>
       </c>
-      <c r="B121" t="inlineStr"/>
       <c r="C121" t="inlineStr">
         <is>
           <t>Scrunchies</t>
@@ -4243,7 +4235,6 @@
       <c r="E121" t="n">
         <v>6</v>
       </c>
-      <c r="F121" t="inlineStr"/>
       <c r="G121" t="inlineStr">
         <is>
           <t>Y</t>
@@ -4261,14 +4252,13 @@
           <t>XXL 30 PC</t>
         </is>
       </c>
-      <c r="B122" t="inlineStr"/>
       <c r="C122" t="inlineStr">
         <is>
           <t>Scrunchies</t>
         </is>
       </c>
       <c r="D122" s="2" t="n">
-        <v>28.5</v>
+        <v>30</v>
       </c>
       <c r="E122" t="n">
         <v>10</v>
@@ -4283,7 +4273,11 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="H122" s="3" t="inlineStr"/>
+      <c r="H122" s="3" t="inlineStr">
+        <is>
+          <t>Rate 24 Oct 2026: ₹28.5 → ₹30.</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -4291,19 +4285,17 @@
           <t>XXL 72 PC RUBED</t>
         </is>
       </c>
-      <c r="B123" t="inlineStr"/>
       <c r="C123" t="inlineStr">
         <is>
           <t>Scrunchies</t>
         </is>
       </c>
       <c r="D123" s="2" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="E123" t="n">
         <v>6</v>
       </c>
-      <c r="F123" t="inlineStr"/>
       <c r="G123" t="inlineStr">
         <is>
           <t>Y</t>
@@ -4311,7 +4303,7 @@
       </c>
       <c r="H123" s="3" t="inlineStr">
         <is>
-          <t>No catalogue photo yet.</t>
+          <t>No catalogue photo yet. Rate 24 Oct 2026: ₹60 → ₹63.</t>
         </is>
       </c>
     </row>
@@ -4321,7 +4313,6 @@
           <t>278</t>
         </is>
       </c>
-      <c r="B124" t="inlineStr"/>
       <c r="C124" t="inlineStr">
         <is>
           <t>Tie Bow</t>
@@ -4351,7 +4342,6 @@
           <t>503</t>
         </is>
       </c>
-      <c r="B125" t="inlineStr"/>
       <c r="C125" t="inlineStr">
         <is>
           <t>Tie Bow</t>
@@ -4415,7 +4405,6 @@
           <t>RC-253</t>
         </is>
       </c>
-      <c r="B127" t="inlineStr"/>
       <c r="C127" t="inlineStr">
         <is>
           <t>Tie Bow</t>
@@ -4445,7 +4434,6 @@
           <t>RC-255</t>
         </is>
       </c>
-      <c r="B128" t="inlineStr"/>
       <c r="C128" t="inlineStr">
         <is>
           <t>Tie Bow</t>
@@ -4475,7 +4463,6 @@
           <t>RC-256</t>
         </is>
       </c>
-      <c r="B129" t="inlineStr"/>
       <c r="C129" t="inlineStr">
         <is>
           <t>Tie Bow</t>
@@ -4505,7 +4492,6 @@
           <t>RC-258</t>
         </is>
       </c>
-      <c r="B130" t="inlineStr"/>
       <c r="C130" t="inlineStr">
         <is>
           <t>Tie Bow</t>
@@ -4535,7 +4521,6 @@
           <t>RC-259</t>
         </is>
       </c>
-      <c r="B131" t="inlineStr"/>
       <c r="C131" t="inlineStr">
         <is>
           <t>Tie Bow</t>
@@ -4565,7 +4550,6 @@
           <t>RC-264</t>
         </is>
       </c>
-      <c r="B132" t="inlineStr"/>
       <c r="C132" t="inlineStr">
         <is>
           <t>Tie Bow</t>
@@ -4595,7 +4579,6 @@
           <t>RC-265</t>
         </is>
       </c>
-      <c r="B133" t="inlineStr"/>
       <c r="C133" t="inlineStr">
         <is>
           <t>Tie Bow</t>
@@ -4625,7 +4608,6 @@
           <t>RC-266</t>
         </is>
       </c>
-      <c r="B134" t="inlineStr"/>
       <c r="C134" t="inlineStr">
         <is>
           <t>Tie Bow</t>
@@ -4655,7 +4637,6 @@
           <t>RC-267</t>
         </is>
       </c>
-      <c r="B135" t="inlineStr"/>
       <c r="C135" t="inlineStr">
         <is>
           <t>Tie Bow</t>
@@ -4685,7 +4666,6 @@
           <t>RC-274</t>
         </is>
       </c>
-      <c r="B136" t="inlineStr"/>
       <c r="C136" t="inlineStr">
         <is>
           <t>Tie Bow</t>
@@ -4715,7 +4695,6 @@
           <t>RC-275</t>
         </is>
       </c>
-      <c r="B137" t="inlineStr"/>
       <c r="C137" t="inlineStr">
         <is>
           <t>Tie Bow</t>
@@ -4834,162 +4813,6 @@
       <c r="H140" s="6" t="inlineStr">
         <is>
           <t>Carton charge, not a product. Keep hidden (or tell us if it should be added to orders).</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" s="7" t="inlineStr"/>
-      <c r="B141" s="7" t="inlineStr"/>
-      <c r="C141" s="7" t="inlineStr">
-        <is>
-          <t>Clutchers</t>
-        </is>
-      </c>
-      <c r="D141" s="8" t="n"/>
-      <c r="E141" s="7" t="n"/>
-      <c r="F141" s="7" t="inlineStr">
-        <is>
-          <t>RC 200</t>
-        </is>
-      </c>
-      <c r="G141" s="7" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H141" s="9" t="inlineStr">
-        <is>
-          <t>Catalogue item with NO rate – fill in Code, Rate and Packet, or leave empty for 'price on request'.</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" s="7" t="inlineStr"/>
-      <c r="B142" s="7" t="inlineStr"/>
-      <c r="C142" s="7" t="inlineStr">
-        <is>
-          <t>Scrunchies</t>
-        </is>
-      </c>
-      <c r="D142" s="8" t="n"/>
-      <c r="E142" s="7" t="n"/>
-      <c r="F142" s="7" t="inlineStr">
-        <is>
-          <t>968</t>
-        </is>
-      </c>
-      <c r="G142" s="7" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H142" s="9" t="inlineStr">
-        <is>
-          <t>Catalogue item with NO rate – fill in Code, Rate and Packet, or leave empty for 'price on request'.</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" s="7" t="inlineStr"/>
-      <c r="B143" s="7" t="inlineStr"/>
-      <c r="C143" s="7" t="inlineStr">
-        <is>
-          <t>Scrunchies</t>
-        </is>
-      </c>
-      <c r="D143" s="8" t="n"/>
-      <c r="E143" s="7" t="n"/>
-      <c r="F143" s="7" t="inlineStr">
-        <is>
-          <t>959</t>
-        </is>
-      </c>
-      <c r="G143" s="7" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H143" s="9" t="inlineStr">
-        <is>
-          <t>Catalogue item with NO rate – fill in Code, Rate and Packet, or leave empty for 'price on request'.</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" s="7" t="inlineStr"/>
-      <c r="B144" s="7" t="inlineStr"/>
-      <c r="C144" s="7" t="inlineStr">
-        <is>
-          <t>Tie Bow</t>
-        </is>
-      </c>
-      <c r="D144" s="8" t="n"/>
-      <c r="E144" s="7" t="n"/>
-      <c r="F144" s="7" t="inlineStr">
-        <is>
-          <t>RC 307</t>
-        </is>
-      </c>
-      <c r="G144" s="7" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H144" s="9" t="inlineStr">
-        <is>
-          <t>Catalogue item with NO rate – fill in Code, Rate and Packet, or leave empty for 'price on request'.</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" s="7" t="inlineStr"/>
-      <c r="B145" s="7" t="inlineStr"/>
-      <c r="C145" s="7" t="inlineStr">
-        <is>
-          <t>Tie Bow</t>
-        </is>
-      </c>
-      <c r="D145" s="8" t="n"/>
-      <c r="E145" s="7" t="n"/>
-      <c r="F145" s="7" t="inlineStr">
-        <is>
-          <t>RC 271</t>
-        </is>
-      </c>
-      <c r="G145" s="7" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H145" s="9" t="inlineStr">
-        <is>
-          <t>Catalogue item with NO rate – fill in Code, Rate and Packet, or leave empty for 'price on request'.</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" s="7" t="inlineStr"/>
-      <c r="B146" s="7" t="inlineStr"/>
-      <c r="C146" s="7" t="inlineStr">
-        <is>
-          <t>Tie Bow</t>
-        </is>
-      </c>
-      <c r="D146" s="8" t="n"/>
-      <c r="E146" s="7" t="n"/>
-      <c r="F146" s="7" t="inlineStr">
-        <is>
-          <t>RC 262</t>
-        </is>
-      </c>
-      <c r="G146" s="7" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H146" s="9" t="inlineStr">
-        <is>
-          <t>Catalogue item with NO rate – fill in Code, Rate and Packet, or leave empty for 'price on request'.</t>
         </is>
       </c>
     </row>
@@ -5017,9 +4840,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-    </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -5076,9 +4897,7 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr"/>
-    </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>

--- a/website/Website Rates (for Google Sheet).xlsx
+++ b/website/Website Rates (for Google Sheet).xlsx
@@ -448,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H140"/>
+  <dimension ref="A1:H116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -511,7 +511,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Fur Chimta</t>
+          <t>Fur Chimta · T-900</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -519,8 +519,8 @@
           <t>Clutchers</t>
         </is>
       </c>
-      <c r="D2" s="2" t="n">
-        <v>102</v>
+      <c r="D2" t="n">
+        <v>105</v>
       </c>
       <c r="E2" t="n">
         <v>4</v>
@@ -535,88 +535,92 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>TESLA · CH-01 (T-900)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>RC-300</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>TESLA-200</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
         <is>
           <t>Fur Chimta</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Clutchers</t>
         </is>
       </c>
-      <c r="D3" s="5" t="n">
-        <v>90</v>
-      </c>
-      <c r="E3" s="4" t="n">
+      <c r="D3" t="n">
+        <v>93</v>
+      </c>
+      <c r="E3" t="n">
         <v>1</v>
       </c>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>RC 200</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>TESLA</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>TESLA-300</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Fur Chimta</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Clutchers</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>93</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" t="inlineStr">
         <is>
           <t>RC 300</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H3" s="6" t="inlineStr">
-        <is>
-          <t>Not the same as scrunchies 300 (₹57).</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>RC-400</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>Fur Chimta</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>Clutchers</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="n">
-        <v>150</v>
-      </c>
-      <c r="E4" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>TESLA 400</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H4" s="6" t="inlineStr">
-        <is>
-          <t>Catalogue page says TESLA 400 – same item as RC-400 fur chimta?</t>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>TESLA</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>RC-500</t>
+          <t>TESLA-500</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -629,8 +633,8 @@
           <t>Clutchers</t>
         </is>
       </c>
-      <c r="D5" s="2" t="n">
-        <v>132</v>
+      <c r="D5" t="n">
+        <v>135</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
@@ -645,12 +649,16 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>TESLA</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>RC-600</t>
+          <t>TESLA-600</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -663,8 +671,8 @@
           <t>Clutchers</t>
         </is>
       </c>
-      <c r="D6" s="2" t="n">
-        <v>126</v>
+      <c r="D6" t="n">
+        <v>129</v>
       </c>
       <c r="E6" t="n">
         <v>1</v>
@@ -679,12 +687,16 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="H6" s="3" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>TESLA</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>RC-700</t>
+          <t>TESLA-700</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -697,8 +709,8 @@
           <t>Clutchers</t>
         </is>
       </c>
-      <c r="D7" s="2" t="n">
-        <v>132</v>
+      <c r="D7" t="n">
+        <v>135</v>
       </c>
       <c r="E7" t="n">
         <v>1</v>
@@ -713,12 +725,21 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>TESLA</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>T-100</t>
+          <t>TESLA-400</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Fur Chimta</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -726,20 +747,25 @@
           <t>Clutchers</t>
         </is>
       </c>
-      <c r="D8" s="2" t="n">
-        <v>72</v>
+      <c r="D8" t="n">
+        <v>153</v>
       </c>
       <c r="E8" t="n">
         <v>1</v>
       </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>TESLA 400</t>
+        </is>
+      </c>
       <c r="G8" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>No catalogue photo yet.</t>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>TESLA</t>
         </is>
       </c>
     </row>
@@ -754,8 +780,8 @@
           <t>Clutchers</t>
         </is>
       </c>
-      <c r="D9" s="2" t="n">
-        <v>60</v>
+      <c r="D9" t="n">
+        <v>63</v>
       </c>
       <c r="E9" t="n">
         <v>6</v>
@@ -770,7 +796,11 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="H9" s="3" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>TESLA</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -783,11 +813,11 @@
           <t>Clutchers</t>
         </is>
       </c>
-      <c r="D10" s="2" t="n">
-        <v>108</v>
+      <c r="D10" t="n">
+        <v>111</v>
       </c>
       <c r="E10" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -799,9 +829,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>Rate 24 Oct 2026: ₹60 → ₹108.</t>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>TESLA</t>
         </is>
       </c>
     </row>
@@ -816,8 +846,8 @@
           <t>Clutchers</t>
         </is>
       </c>
-      <c r="D11" s="2" t="n">
-        <v>45</v>
+      <c r="D11" t="n">
+        <v>48</v>
       </c>
       <c r="E11" t="n">
         <v>6</v>
@@ -832,7 +862,11 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="H11" s="3" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>TESLA</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -845,8 +879,8 @@
           <t>Clutchers</t>
         </is>
       </c>
-      <c r="D12" s="2" t="n">
-        <v>84</v>
+      <c r="D12" t="n">
+        <v>87</v>
       </c>
       <c r="E12" t="n">
         <v>4</v>
@@ -861,12 +895,16 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="H12" s="3" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>TESLA</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>TESLA-710</t>
+          <t>TESLA-711</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -874,15 +912,15 @@
           <t>Clutchers</t>
         </is>
       </c>
-      <c r="D13" s="2" t="n">
-        <v>126</v>
+      <c r="D13" t="n">
+        <v>66</v>
       </c>
       <c r="E13" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>TESLA 710</t>
+          <t>TESLA 711</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -890,12 +928,16 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="H13" s="3" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>TESLA</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>TESLA-711</t>
+          <t>TESLA-713</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -903,15 +945,15 @@
           <t>Clutchers</t>
         </is>
       </c>
-      <c r="D14" s="2" t="n">
-        <v>63</v>
+      <c r="D14" t="n">
+        <v>105</v>
       </c>
       <c r="E14" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>TESLA 711</t>
+          <t>TESLA 713</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -919,12 +961,16 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="H14" s="3" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>TESLA</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>TESLA-712</t>
+          <t>TESLA-714</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -932,15 +978,15 @@
           <t>Clutchers</t>
         </is>
       </c>
-      <c r="D15" s="2" t="n">
-        <v>72</v>
+      <c r="D15" t="n">
+        <v>69</v>
       </c>
       <c r="E15" t="n">
         <v>4</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>TESLA 712</t>
+          <t>TESLA 714</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -948,12 +994,16 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="H15" s="3" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>TESLA</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>TESLA-713</t>
+          <t>TESLA-716</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -961,15 +1011,15 @@
           <t>Clutchers</t>
         </is>
       </c>
-      <c r="D16" s="2" t="n">
-        <v>102</v>
+      <c r="D16" t="n">
+        <v>87</v>
       </c>
       <c r="E16" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>TESLA 713</t>
+          <t>TESLA 716</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -977,12 +1027,16 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="H16" s="3" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>TESLA</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>TESLA-714</t>
+          <t>TESLA-717</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -990,15 +1044,15 @@
           <t>Clutchers</t>
         </is>
       </c>
-      <c r="D17" s="2" t="n">
-        <v>66</v>
+      <c r="D17" t="n">
+        <v>93</v>
       </c>
       <c r="E17" t="n">
         <v>4</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>TESLA 714</t>
+          <t>TESLA 717</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1006,17 +1060,16 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="H17" s="3" t="inlineStr"/>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>TESLA</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>TESLA-715</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>R.M</t>
+          <t>TESLA-718</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1024,15 +1077,15 @@
           <t>Clutchers</t>
         </is>
       </c>
-      <c r="D18" s="2" t="n">
-        <v>114</v>
+      <c r="D18" t="n">
+        <v>57</v>
       </c>
       <c r="E18" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>TESLA 715</t>
+          <t>TESLA 718</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1040,12 +1093,16 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="H18" s="3" t="inlineStr"/>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>TESLA</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>TESLA-716</t>
+          <t>TESLA-719</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1053,15 +1110,15 @@
           <t>Clutchers</t>
         </is>
       </c>
-      <c r="D19" s="2" t="n">
-        <v>84</v>
+      <c r="D19" t="n">
+        <v>90</v>
       </c>
       <c r="E19" t="n">
         <v>4</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>TESLA 716</t>
+          <t>TESLA 719</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1069,12 +1126,16 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="H19" s="3" t="inlineStr"/>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>TESLA</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>TESLA-717</t>
+          <t>TESLA-722</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1082,15 +1143,15 @@
           <t>Clutchers</t>
         </is>
       </c>
-      <c r="D20" s="2" t="n">
-        <v>90</v>
+      <c r="D20" t="n">
+        <v>129</v>
       </c>
       <c r="E20" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>TESLA 717</t>
+          <t>TESLA 722</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1098,12 +1159,16 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="H20" s="3" t="inlineStr"/>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>TESLA</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>TESLA-718</t>
+          <t>TESLA-751</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1111,15 +1176,15 @@
           <t>Clutchers</t>
         </is>
       </c>
-      <c r="D21" s="2" t="n">
-        <v>54</v>
+      <c r="D21" t="n">
+        <v>84</v>
       </c>
       <c r="E21" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>TESLA 718</t>
+          <t>TESLA 751</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1127,12 +1192,16 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="H21" s="3" t="inlineStr"/>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>TESLA</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>TESLA-719</t>
+          <t>TESLA-752</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1140,15 +1209,15 @@
           <t>Clutchers</t>
         </is>
       </c>
-      <c r="D22" s="2" t="n">
-        <v>87</v>
+      <c r="D22" t="n">
+        <v>75</v>
       </c>
       <c r="E22" t="n">
         <v>4</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>TESLA 719</t>
+          <t>TESLA 752</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1156,17 +1225,16 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="H22" s="3" t="inlineStr"/>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>TESLA</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>TESLA-720</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>R.M</t>
+          <t>TESLA-753</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1174,15 +1242,15 @@
           <t>Clutchers</t>
         </is>
       </c>
-      <c r="D23" s="2" t="n">
-        <v>102</v>
+      <c r="D23" t="n">
+        <v>63</v>
       </c>
       <c r="E23" t="n">
         <v>4</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>TESLA 720</t>
+          <t>TESLA 753</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1190,17 +1258,16 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="H23" s="3" t="inlineStr"/>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>TESLA</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>TESLA-721</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>R.M</t>
+          <t>TESLA-712</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1208,27 +1275,37 @@
           <t>Clutchers</t>
         </is>
       </c>
-      <c r="D24" s="2" t="n">
-        <v>78</v>
+      <c r="D24" t="n">
+        <v>75</v>
       </c>
       <c r="E24" t="n">
         <v>4</v>
       </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>TESLA 712</t>
+        </is>
+      </c>
       <c r="G24" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="H24" s="3" t="inlineStr">
-        <is>
-          <t>No catalogue photo yet. Rate 24 Oct 2026: ₹81 → ₹78.</t>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>TESLA</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>TESLA-722</t>
+          <t>TESLA-RM 712</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Rubber matt</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1236,15 +1313,15 @@
           <t>Clutchers</t>
         </is>
       </c>
-      <c r="D25" s="2" t="n">
-        <v>126</v>
+      <c r="D25" t="n">
+        <v>93</v>
       </c>
       <c r="E25" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>TESLA 722</t>
+          <t>TESLA 712</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1252,12 +1329,21 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="H25" s="3" t="inlineStr"/>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>TESLA · TESLA-RM (712)</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>TESLA-751</t>
+          <t>TESLA-715</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>R.M</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1265,15 +1351,15 @@
           <t>Clutchers</t>
         </is>
       </c>
-      <c r="D26" s="2" t="n">
-        <v>81</v>
+      <c r="D26" t="n">
+        <v>117</v>
       </c>
       <c r="E26" t="n">
         <v>4</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>TESLA 751</t>
+          <t>TESLA 715</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1281,12 +1367,21 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="H26" s="3" t="inlineStr"/>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>TESLA · TESLA-715 R.M</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>TESLA-752</t>
+          <t>TESLA-720</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>R.M</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1294,15 +1389,15 @@
           <t>Clutchers</t>
         </is>
       </c>
-      <c r="D27" s="2" t="n">
-        <v>72</v>
+      <c r="D27" t="n">
+        <v>105</v>
       </c>
       <c r="E27" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>TESLA 752</t>
+          <t>TESLA 720</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1310,12 +1405,21 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="H27" s="3" t="inlineStr"/>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>TESLA · TESLA-720 R.M</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>TESLA-753</t>
+          <t>CH-50</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Fur Chimta · T-800</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1323,66 +1427,60 @@
           <t>Clutchers</t>
         </is>
       </c>
-      <c r="D28" s="2" t="n">
-        <v>60</v>
+      <c r="D28" t="n">
+        <v>81</v>
       </c>
       <c r="E28" t="n">
         <v>4</v>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>TESLA 753</t>
-        </is>
-      </c>
       <c r="G28" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="H28" s="3" t="inlineStr"/>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>TESLA · CH-50 (T-800)</t>
+        </is>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
-          <t>TESLA-RM 712</t>
-        </is>
-      </c>
-      <c r="B29" s="4" t="inlineStr">
-        <is>
-          <t>Rubber matt</t>
-        </is>
-      </c>
-      <c r="C29" s="4" t="inlineStr">
-        <is>
-          <t>Clutchers</t>
-        </is>
-      </c>
-      <c r="D29" s="5" t="n">
-        <v>90</v>
-      </c>
-      <c r="E29" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="F29" s="4" t="inlineStr">
-        <is>
-          <t>TESLA 712</t>
-        </is>
-      </c>
-      <c r="G29" s="4" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H29" s="6" t="inlineStr">
-        <is>
-          <t>Same item as TESLA-712 (₹72)? If yes, delete one row.</t>
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>322</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Scrunchies</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>57</v>
+      </c>
+      <c r="E29" t="n">
+        <v>6</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>322</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>RAJ GOLD BOX</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>100 PC NYLON RUBBER</t>
+          <t>349</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1390,61 +1488,65 @@
           <t>Scrunchies</t>
         </is>
       </c>
-      <c r="D30" s="2" t="n">
-        <v>66</v>
+      <c r="D30" t="n">
+        <v>57</v>
       </c>
       <c r="E30" t="n">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>349</t>
+        </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="H30" s="3" t="inlineStr">
-        <is>
-          <t>No catalogue photo yet.</t>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>RAJ GOLD BOX</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="4" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="B31" s="4" t="inlineStr"/>
-      <c r="C31" s="4" t="inlineStr">
-        <is>
-          <t>Scrunchies</t>
-        </is>
-      </c>
-      <c r="D31" s="5" t="n">
-        <v>60</v>
-      </c>
-      <c r="E31" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F31" s="4" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="G31" s="4" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H31" s="6" t="inlineStr">
-        <is>
-          <t>Not the same as RC-300 fur chimta (clutchers, ₹90). Rate 24 Oct 2026: ₹57 → ₹60.</t>
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>355</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Scrunchies</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>81</v>
+      </c>
+      <c r="E31" t="n">
+        <v>4</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>355</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>RAJ GOLD BOX</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>322</t>
+          <t>903</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1452,15 +1554,15 @@
           <t>Scrunchies</t>
         </is>
       </c>
-      <c r="D32" s="2" t="n">
-        <v>54</v>
+      <c r="D32" t="n">
+        <v>81</v>
       </c>
       <c r="E32" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>322</t>
+          <t>903</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -1468,12 +1570,16 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="H32" s="3" t="inlineStr"/>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>JUMBO BOX</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>335</t>
+          <t>920</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1481,15 +1587,15 @@
           <t>Scrunchies</t>
         </is>
       </c>
-      <c r="D33" s="2" t="n">
-        <v>37.5</v>
+      <c r="D33" t="n">
+        <v>75</v>
       </c>
       <c r="E33" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>335</t>
+          <t>920</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -1497,16 +1603,16 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="H33" s="3" t="inlineStr">
-        <is>
-          <t>Rate 24 Oct 2026: ₹36 → ₹37.5.</t>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>ITC BOX</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>349</t>
+          <t>931</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1514,15 +1620,15 @@
           <t>Scrunchies</t>
         </is>
       </c>
-      <c r="D34" s="2" t="n">
-        <v>54</v>
+      <c r="D34" t="n">
+        <v>45</v>
       </c>
       <c r="E34" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>349</t>
+          <t>931</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -1530,12 +1636,16 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="H34" s="3" t="inlineStr"/>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>JUMBO BOX</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>355</t>
+          <t>934</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1543,15 +1653,15 @@
           <t>Scrunchies</t>
         </is>
       </c>
-      <c r="D35" s="2" t="n">
-        <v>78</v>
+      <c r="D35" t="n">
+        <v>57</v>
       </c>
       <c r="E35" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>355</t>
+          <t>934</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -1559,12 +1669,16 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="H35" s="3" t="inlineStr"/>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>ITC BOX</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>36 PC NYLON RUBBER</t>
+          <t>980</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1572,62 +1686,65 @@
           <t>Scrunchies</t>
         </is>
       </c>
-      <c r="D36" s="2" t="n">
-        <v>25.5</v>
+      <c r="D36" t="n">
+        <v>81</v>
       </c>
       <c r="E36" t="n">
+        <v>4</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>980</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>JUMBO BOX</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>952</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Scrunchies</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>75</v>
+      </c>
+      <c r="E37" t="n">
         <v>6</v>
       </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>36 PC NYLON RUBBER</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H36" s="3" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="4" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="B37" s="4" t="inlineStr"/>
-      <c r="C37" s="4" t="inlineStr">
-        <is>
-          <t>Scrunchies</t>
-        </is>
-      </c>
-      <c r="D37" s="5" t="n">
-        <v>66</v>
-      </c>
-      <c r="E37" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="F37" s="4" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="G37" s="4" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H37" s="6" t="inlineStr">
-        <is>
-          <t>Not the same as RC-400 fur chimta (clutchers, ₹150). Rate 24 Oct 2026: ₹63 → ₹66.</t>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>952</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>ITC BOX</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>430</t>
+          <t>960</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1635,27 +1752,32 @@
           <t>Scrunchies</t>
         </is>
       </c>
-      <c r="D38" s="2" t="n">
-        <v>72</v>
+      <c r="D38" t="n">
+        <v>75</v>
       </c>
       <c r="E38" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>960</t>
+        </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="H38" s="3" t="inlineStr">
-        <is>
-          <t>No catalogue photo yet.</t>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>JUMBO BOX</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>432</t>
+          <t>968</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1663,15 +1785,15 @@
           <t>Scrunchies</t>
         </is>
       </c>
-      <c r="D39" s="2" t="n">
-        <v>108</v>
+      <c r="D39" t="n">
+        <v>39</v>
       </c>
       <c r="E39" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>RC 432</t>
+          <t>968</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -1679,12 +1801,16 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="H39" s="3" t="inlineStr"/>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>ITC BOX</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>433</t>
+          <t>965</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1692,15 +1818,15 @@
           <t>Scrunchies</t>
         </is>
       </c>
-      <c r="D40" s="2" t="n">
-        <v>78</v>
+      <c r="D40" t="n">
+        <v>45</v>
       </c>
       <c r="E40" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>RC 433</t>
+          <t>965</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -1708,12 +1834,16 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="H40" s="3" t="inlineStr"/>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>ITC BOX</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>434</t>
+          <t>993</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1721,15 +1851,15 @@
           <t>Scrunchies</t>
         </is>
       </c>
-      <c r="D41" s="2" t="n">
-        <v>102</v>
+      <c r="D41" t="n">
+        <v>63</v>
       </c>
       <c r="E41" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>RC 434</t>
+          <t>993</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -1737,12 +1867,16 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="H41" s="3" t="inlineStr"/>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>ITC BOX</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>437</t>
+          <t>940</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1750,27 +1884,32 @@
           <t>Scrunchies</t>
         </is>
       </c>
-      <c r="D42" s="2" t="n">
-        <v>78</v>
+      <c r="D42" t="n">
+        <v>66</v>
       </c>
       <c r="E42" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>940</t>
+        </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="H42" s="3" t="inlineStr">
-        <is>
-          <t>No catalogue photo yet.</t>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>ITC BOX</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>438</t>
+          <t>959</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1778,15 +1917,15 @@
           <t>Scrunchies</t>
         </is>
       </c>
-      <c r="D43" s="2" t="n">
-        <v>36</v>
+      <c r="D43" t="n">
+        <v>75</v>
       </c>
       <c r="E43" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>RC 438</t>
+          <t>959</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -1794,42 +1933,49 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="H43" s="3" t="inlineStr"/>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>JUMBO BOX</t>
+        </is>
+      </c>
     </row>
     <row r="44">
-      <c r="A44" s="4" t="inlineStr">
-        <is>
-          <t>511</t>
-        </is>
-      </c>
-      <c r="B44" s="4" t="inlineStr"/>
-      <c r="C44" s="4" t="inlineStr">
-        <is>
-          <t>Scrunchies</t>
-        </is>
-      </c>
-      <c r="D44" s="5" t="n">
-        <v>33</v>
-      </c>
-      <c r="E44" s="4" t="n">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>996</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Scrunchies</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>60</v>
+      </c>
+      <c r="E44" t="n">
         <v>5</v>
       </c>
-      <c r="F44" s="4" t="inlineStr"/>
-      <c r="G44" s="4" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H44" s="6" t="inlineStr">
-        <is>
-          <t>Different from RC-511 tie bow (₹96)? No catalogue photo.</t>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>996</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>ITC BOX</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>903</t>
+          <t>967</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1837,15 +1983,15 @@
           <t>Scrunchies</t>
         </is>
       </c>
-      <c r="D45" s="2" t="n">
-        <v>78</v>
+      <c r="D45" t="n">
+        <v>87</v>
       </c>
       <c r="E45" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>903</t>
+          <t>967</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -1853,12 +1999,16 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="H45" s="3" t="inlineStr"/>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>ITC BOX</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>912</t>
+          <t>335</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1866,27 +2016,32 @@
           <t>Scrunchies</t>
         </is>
       </c>
-      <c r="D46" s="2" t="n">
-        <v>72</v>
+      <c r="D46" t="n">
+        <v>40.5</v>
       </c>
       <c r="E46" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>335</t>
+        </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="H46" s="3" t="inlineStr">
-        <is>
-          <t>No catalogue photo yet.</t>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>TRISHONA - 4</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>913</t>
+          <t>998</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1894,27 +2049,32 @@
           <t>Scrunchies</t>
         </is>
       </c>
-      <c r="D47" s="2" t="n">
+      <c r="D47" t="n">
         <v>66</v>
       </c>
       <c r="E47" t="n">
         <v>5</v>
       </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>998</t>
+        </is>
+      </c>
       <c r="G47" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="H47" s="3" t="inlineStr">
-        <is>
-          <t>No catalogue photo yet.</t>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>ITC BOX</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>914</t>
+          <t>400</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1922,27 +2082,32 @@
           <t>Scrunchies</t>
         </is>
       </c>
-      <c r="D48" s="2" t="n">
+      <c r="D48" t="n">
         <v>69</v>
       </c>
       <c r="E48" t="n">
-        <v>6</v>
+        <v>8</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="H48" s="3" t="inlineStr">
-        <is>
-          <t>No catalogue photo yet.</t>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>RAJ  I  WINDOW</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>917</t>
+          <t>432</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1950,27 +2115,32 @@
           <t>Scrunchies</t>
         </is>
       </c>
-      <c r="D49" s="2" t="n">
-        <v>72</v>
+      <c r="D49" t="n">
+        <v>111</v>
       </c>
       <c r="E49" t="n">
-        <v>5</v>
+        <v>4</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>RC 432</t>
+        </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="H49" s="3" t="inlineStr">
-        <is>
-          <t>No catalogue photo yet.</t>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>RAJ  I  WINDOW</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>920</t>
+          <t>433</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1978,15 +2148,15 @@
           <t>Scrunchies</t>
         </is>
       </c>
-      <c r="D50" s="2" t="n">
-        <v>72</v>
+      <c r="D50" t="n">
+        <v>81</v>
       </c>
       <c r="E50" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>920</t>
+          <t>RC 433</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -1994,12 +2164,16 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="H50" s="3" t="inlineStr"/>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>RAJ  I  WINDOW</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>931</t>
+          <t>434</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2007,15 +2181,15 @@
           <t>Scrunchies</t>
         </is>
       </c>
-      <c r="D51" s="2" t="n">
-        <v>42</v>
+      <c r="D51" t="n">
+        <v>105</v>
       </c>
       <c r="E51" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>931</t>
+          <t>RC 434</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -2023,12 +2197,16 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="H51" s="3" t="inlineStr"/>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>RAJ  I  WINDOW</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>933</t>
+          <t>438</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2036,27 +2214,37 @@
           <t>Scrunchies</t>
         </is>
       </c>
-      <c r="D52" s="2" t="n">
-        <v>66</v>
+      <c r="D52" t="n">
+        <v>39</v>
       </c>
       <c r="E52" t="n">
-        <v>6</v>
+        <v>8</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>RC 438</t>
+        </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="H52" s="3" t="inlineStr">
-        <is>
-          <t>No catalogue photo yet.</t>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>RAJ  I  WINDOW</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>934</t>
+          <t>RT-601</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Tier Rubed</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2064,15 +2252,15 @@
           <t>Scrunchies</t>
         </is>
       </c>
-      <c r="D53" s="2" t="n">
-        <v>54</v>
+      <c r="D53" t="n">
+        <v>78</v>
       </c>
       <c r="E53" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>934</t>
+          <t>RC-601</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -2080,12 +2268,21 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="H53" s="3" t="inlineStr"/>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>RT-600</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>940</t>
+          <t>RT-613</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>12 pc · Tier Rubed</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2093,15 +2290,15 @@
           <t>Scrunchies</t>
         </is>
       </c>
-      <c r="D54" s="2" t="n">
-        <v>63</v>
+      <c r="D54" t="n">
+        <v>34.5</v>
       </c>
       <c r="E54" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>940</t>
+          <t>T-613</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -2109,12 +2306,16 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="H54" s="3" t="inlineStr"/>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>RT-600</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>941</t>
+          <t>RT-614</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2122,27 +2323,32 @@
           <t>Scrunchies</t>
         </is>
       </c>
-      <c r="D55" s="2" t="n">
-        <v>66</v>
+      <c r="D55" t="n">
+        <v>34.5</v>
       </c>
       <c r="E55" t="n">
-        <v>5</v>
+        <v>10</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>T-614</t>
+        </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="H55" s="3" t="inlineStr">
-        <is>
-          <t>No catalogue photo yet.</t>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>RT-600</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>945</t>
+          <t>RT-618</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2150,27 +2356,32 @@
           <t>Scrunchies</t>
         </is>
       </c>
-      <c r="D56" s="2" t="n">
-        <v>72</v>
+      <c r="D56" t="n">
+        <v>54</v>
       </c>
       <c r="E56" t="n">
-        <v>6</v>
+        <v>10</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>T-618</t>
+        </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="H56" s="3" t="inlineStr">
-        <is>
-          <t>No catalogue photo yet.</t>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>RT-600</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>952</t>
+          <t>RT-619</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2178,15 +2389,15 @@
           <t>Scrunchies</t>
         </is>
       </c>
-      <c r="D57" s="2" t="n">
-        <v>72</v>
+      <c r="D57" t="n">
+        <v>39</v>
       </c>
       <c r="E57" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>952</t>
+          <t>T-619</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -2194,12 +2405,16 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="H57" s="3" t="inlineStr"/>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>RT-600</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>960</t>
+          <t>RT-617</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2207,15 +2422,15 @@
           <t>Scrunchies</t>
         </is>
       </c>
-      <c r="D58" s="2" t="n">
-        <v>72</v>
+      <c r="D58" t="n">
+        <v>147</v>
       </c>
       <c r="E58" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>960</t>
+          <t>RC-617</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -2223,12 +2438,21 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="H58" s="3" t="inlineStr"/>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>RT-600</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>965</t>
+          <t>RT-605</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>36 pc · Rabit Fur</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2236,15 +2460,15 @@
           <t>Scrunchies</t>
         </is>
       </c>
-      <c r="D59" s="2" t="n">
-        <v>42</v>
+      <c r="D59" t="n">
+        <v>87</v>
       </c>
       <c r="E59" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>965</t>
+          <t>RC-605</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -2252,16 +2476,16 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="H59" s="3" t="inlineStr">
-        <is>
-          <t>Rate 24 Oct 2026: ₹39 → ₹42.</t>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>RT-600</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>967</t>
+          <t>BS-01</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2269,15 +2493,15 @@
           <t>Scrunchies</t>
         </is>
       </c>
-      <c r="D60" s="2" t="n">
-        <v>84</v>
+      <c r="D60" t="n">
+        <v>60</v>
       </c>
       <c r="E60" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>967</t>
+          <t>BS-01</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -2285,12 +2509,16 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="H60" s="3" t="inlineStr"/>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>NISAR</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>980</t>
+          <t>BS-02</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2298,15 +2526,15 @@
           <t>Scrunchies</t>
         </is>
       </c>
-      <c r="D61" s="2" t="n">
-        <v>78</v>
+      <c r="D61" t="n">
+        <v>87</v>
       </c>
       <c r="E61" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>980</t>
+          <t>BS-02</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -2314,12 +2542,16 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="H61" s="3" t="inlineStr"/>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>NISAR</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>986</t>
+          <t>BS-03</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2327,15 +2559,15 @@
           <t>Scrunchies</t>
         </is>
       </c>
-      <c r="D62" s="2" t="n">
-        <v>84</v>
+      <c r="D62" t="n">
+        <v>108</v>
       </c>
       <c r="E62" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>986</t>
+          <t>BS-03</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -2343,12 +2575,16 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="H62" s="3" t="inlineStr"/>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>NISAR</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>991</t>
+          <t>MOBILON</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2356,15 +2592,15 @@
           <t>Scrunchies</t>
         </is>
       </c>
-      <c r="D63" s="2" t="n">
-        <v>102</v>
+      <c r="D63" t="n">
+        <v>108</v>
       </c>
       <c r="E63" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>991</t>
+          <t>MOBILON</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -2372,12 +2608,16 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="H63" s="3" t="inlineStr"/>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>UNIQUE MODEL</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>993</t>
+          <t>D-02</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2385,15 +2625,15 @@
           <t>Scrunchies</t>
         </is>
       </c>
-      <c r="D64" s="2" t="n">
-        <v>60</v>
+      <c r="D64" t="n">
+        <v>20</v>
       </c>
       <c r="E64" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>993</t>
+          <t>D-02</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -2401,16 +2641,16 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="H64" s="3" t="inlineStr">
-        <is>
-          <t>Rate 24 Oct 2026: ₹57 → ₹60.</t>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>BOTTLES</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>996</t>
+          <t>D-03</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2418,15 +2658,15 @@
           <t>Scrunchies</t>
         </is>
       </c>
-      <c r="D65" s="2" t="n">
-        <v>57</v>
+      <c r="D65" t="n">
+        <v>18</v>
       </c>
       <c r="E65" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>996</t>
+          <t>D-03</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -2434,16 +2674,16 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="H65" s="3" t="inlineStr">
-        <is>
-          <t>Rate 24 Oct 2026: ₹54 → ₹57.</t>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>BOTTLES</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>998</t>
+          <t>D-04</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2451,15 +2691,15 @@
           <t>Scrunchies</t>
         </is>
       </c>
-      <c r="D66" s="2" t="n">
-        <v>63</v>
+      <c r="D66" t="n">
+        <v>20</v>
       </c>
       <c r="E66" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>998</t>
+          <t>D-04</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -2467,16 +2707,16 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="H66" s="3" t="inlineStr">
-        <is>
-          <t>Rate 24 Oct 2026: ₹60 → ₹63.</t>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>BOTTLES</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>BS-01</t>
+          <t>D-05</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2484,15 +2724,15 @@
           <t>Scrunchies</t>
         </is>
       </c>
-      <c r="D67" s="2" t="n">
-        <v>57</v>
+      <c r="D67" t="n">
+        <v>17</v>
       </c>
       <c r="E67" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>BS-01</t>
+          <t>D-05</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -2500,16 +2740,16 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="H67" s="3" t="inlineStr">
-        <is>
-          <t>Rate 24 Oct 2026: ₹58.5 → ₹57.</t>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>BOTTLES</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>BS-02</t>
+          <t>D-06</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2517,15 +2757,15 @@
           <t>Scrunchies</t>
         </is>
       </c>
-      <c r="D68" s="2" t="n">
-        <v>84</v>
+      <c r="D68" t="n">
+        <v>17</v>
       </c>
       <c r="E68" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>BS-02</t>
+          <t>D-06</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -2533,12 +2773,16 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="H68" s="3" t="inlineStr"/>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>BOTTLES</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>BS-03</t>
+          <t>D-07</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2546,15 +2790,15 @@
           <t>Scrunchies</t>
         </is>
       </c>
-      <c r="D69" s="2" t="n">
-        <v>105</v>
+      <c r="D69" t="n">
+        <v>36</v>
       </c>
       <c r="E69" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>BS-03</t>
+          <t>D-07</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -2562,16 +2806,16 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="H69" s="3" t="inlineStr">
-        <is>
-          <t>Rate 24 Oct 2026: ₹114 → ₹105.</t>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>BOTTLES</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>D-01</t>
+          <t>D-08</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2579,27 +2823,32 @@
           <t>Scrunchies</t>
         </is>
       </c>
-      <c r="D70" s="2" t="n">
-        <v>17</v>
+      <c r="D70" t="n">
+        <v>16</v>
       </c>
       <c r="E70" t="n">
         <v>12</v>
       </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>D-08</t>
+        </is>
+      </c>
       <c r="G70" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="H70" s="3" t="inlineStr">
-        <is>
-          <t>No catalogue photo yet. Rate 24 Oct 2026: ₹16 → ₹17.</t>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>BOTTLES</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>D-02</t>
+          <t>D-10</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2607,15 +2856,15 @@
           <t>Scrunchies</t>
         </is>
       </c>
-      <c r="D71" s="2" t="n">
-        <v>17</v>
+      <c r="D71" t="n">
+        <v>20</v>
       </c>
       <c r="E71" t="n">
         <v>12</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>D-02</t>
+          <t>D-10</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -2623,16 +2872,16 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="H71" s="3" t="inlineStr">
-        <is>
-          <t>Rate 24 Oct 2026: ₹16 → ₹17.</t>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>BOTTLES</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>D-03</t>
+          <t>SUMO-RINKLE</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2640,15 +2889,15 @@
           <t>Scrunchies</t>
         </is>
       </c>
-      <c r="D72" s="2" t="n">
-        <v>15</v>
+      <c r="D72" t="n">
+        <v>117</v>
       </c>
       <c r="E72" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>D-03</t>
+          <t>SUMO RINKLE</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -2656,12 +2905,16 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="H72" s="3" t="inlineStr"/>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>JUMBO BOX</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>D-04</t>
+          <t>RC-202</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2669,15 +2922,15 @@
           <t>Scrunchies</t>
         </is>
       </c>
-      <c r="D73" s="2" t="n">
-        <v>17</v>
+      <c r="D73" t="n">
+        <v>159</v>
       </c>
       <c r="E73" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>D-04</t>
+          <t>202</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -2685,16 +2938,16 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="H73" s="3" t="inlineStr">
-        <is>
-          <t>Rate 24 Oct 2026: ₹16 → ₹17.</t>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>RAJ FANCY</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>D-05</t>
+          <t>J.J. JUMBO</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2702,15 +2955,15 @@
           <t>Scrunchies</t>
         </is>
       </c>
-      <c r="D74" s="2" t="n">
-        <v>14</v>
+      <c r="D74" t="n">
+        <v>105</v>
       </c>
       <c r="E74" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>D-05</t>
+          <t>GEORGETTE JUMBO</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -2718,12 +2971,21 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="H74" s="3" t="inlineStr"/>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>JUMBO BOX</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>D-06</t>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Gift Box</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2731,15 +2993,15 @@
           <t>Scrunchies</t>
         </is>
       </c>
-      <c r="D75" s="2" t="n">
-        <v>14</v>
+      <c r="D75" t="n">
+        <v>84</v>
       </c>
       <c r="E75" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>D-06</t>
+          <t>100 GIFT BOX</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -2747,16 +3009,16 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="H75" s="3" t="inlineStr">
-        <is>
-          <t>Rate 24 Oct 2026: ₹13.5 → ₹14.</t>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>JUMBO BOX</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>D-07</t>
+          <t>300</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2764,15 +3026,15 @@
           <t>Scrunchies</t>
         </is>
       </c>
-      <c r="D76" s="2" t="n">
-        <v>33</v>
+      <c r="D76" t="n">
+        <v>63</v>
       </c>
       <c r="E76" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>D-07</t>
+          <t>300</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -2780,12 +3042,16 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="H76" s="3" t="inlineStr"/>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>JUMBO BOX</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>D-08</t>
+          <t>RJ-1001</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2793,15 +3059,15 @@
           <t>Scrunchies</t>
         </is>
       </c>
-      <c r="D77" s="2" t="n">
-        <v>13</v>
+      <c r="D77" t="n">
+        <v>99</v>
       </c>
       <c r="E77" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>D-08</t>
+          <t>1001</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -2809,16 +3075,16 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="H77" s="3" t="inlineStr">
-        <is>
-          <t>Rate 24 Oct 2026: ₹12 → ₹13.</t>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>1000-RAJ</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>D-09</t>
+          <t>RJ-1002</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2826,27 +3092,32 @@
           <t>Scrunchies</t>
         </is>
       </c>
-      <c r="D78" s="2" t="n">
-        <v>21</v>
+      <c r="D78" t="n">
+        <v>105</v>
       </c>
       <c r="E78" t="n">
-        <v>12</v>
+        <v>6</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>1002</t>
+        </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="H78" s="3" t="inlineStr">
-        <is>
-          <t>No catalogue photo yet.</t>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>1000-RAJ</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>D-10</t>
+          <t>RJ-1003</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2854,15 +3125,15 @@
           <t>Scrunchies</t>
         </is>
       </c>
-      <c r="D79" s="2" t="n">
-        <v>17</v>
+      <c r="D79" t="n">
+        <v>111</v>
       </c>
       <c r="E79" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>D-10</t>
+          <t>1003</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -2870,118 +3141,130 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="H79" s="3" t="inlineStr">
-        <is>
-          <t>Rate 24 Oct 2026: ₹16 → ₹17.</t>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>1000-RAJ</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="4" t="inlineStr">
-        <is>
-          <t>J.J. JUMBO</t>
-        </is>
-      </c>
-      <c r="B80" s="4" t="inlineStr"/>
-      <c r="C80" s="4" t="inlineStr">
-        <is>
-          <t>Scrunchies</t>
-        </is>
-      </c>
-      <c r="D80" s="5" t="n">
-        <v>102</v>
-      </c>
-      <c r="E80" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="F80" s="4" t="inlineStr">
-        <is>
-          <t>GEORGETTE JUMBO</t>
-        </is>
-      </c>
-      <c r="G80" s="4" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H80" s="6" t="inlineStr">
-        <is>
-          <t>Is GEORGETTE JUMBO (catalogue) = J.J. JUMBO? Listed twice: pkt 4 here, pkt 1 in the other row.</t>
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>RJ-1004</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Scrunchies</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>57</v>
+      </c>
+      <c r="E80" t="n">
+        <v>6</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>1004</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>1000-RAJ</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="4" t="inlineStr">
-        <is>
-          <t>J.J.JUMBO</t>
-        </is>
-      </c>
-      <c r="B81" s="4" t="inlineStr"/>
-      <c r="C81" s="4" t="inlineStr">
-        <is>
-          <t>Scrunchies</t>
-        </is>
-      </c>
-      <c r="D81" s="5" t="n">
-        <v>102</v>
-      </c>
-      <c r="E81" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F81" s="4" t="inlineStr">
-        <is>
-          <t>GEORGETTE JUMBO</t>
-        </is>
-      </c>
-      <c r="G81" s="4" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H81" s="6" t="inlineStr">
-        <is>
-          <t>Duplicate of J.J. JUMBO but packet 1 instead of 4 – which is right? Delete the wrong row.</t>
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>RT-1</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Hair bun donut · 5 g</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Scrunchies</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>72</v>
+      </c>
+      <c r="E81" t="n">
+        <v>10</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>BUN DONUT</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>DONET · RT-1 ( 5 GRM )</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="4" t="inlineStr">
-        <is>
-          <t>MOBILON</t>
-        </is>
-      </c>
-      <c r="B82" s="4" t="inlineStr"/>
-      <c r="C82" s="4" t="inlineStr">
-        <is>
-          <t>Scrunchies</t>
-        </is>
-      </c>
-      <c r="D82" s="5" t="n">
-        <v>105</v>
-      </c>
-      <c r="E82" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F82" s="4" t="inlineStr">
-        <is>
-          <t>MOBILON</t>
-        </is>
-      </c>
-      <c r="G82" s="4" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H82" s="6" t="inlineStr">
-        <is>
-          <t>Or is the catalogue MOBILON page RC-610 (MOBILON RUBBER)?</t>
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>RT-2</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Hair bun donut · 8 g</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Scrunchies</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>81</v>
+      </c>
+      <c r="E82" t="n">
+        <v>10</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>BUN DONUT</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>DONET · RT-2 ( 8 GRM )</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>MOBILON CARD</t>
+          <t>RT-3</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Hair bun donut · 10 g</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -2989,27 +3272,37 @@
           <t>Scrunchies</t>
         </is>
       </c>
-      <c r="D83" s="2" t="n">
-        <v>24</v>
+      <c r="D83" t="n">
+        <v>90</v>
       </c>
       <c r="E83" t="n">
-        <v>12</v>
+        <v>10</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>BUN DONUT</t>
+        </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="H83" s="3" t="inlineStr">
-        <is>
-          <t>No catalogue photo yet.</t>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>DONET · RT-3 ( 10 GRM )</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>PS-01</t>
+          <t>RT-4</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Hair bun donut · 12 g</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3017,32 +3310,37 @@
           <t>Scrunchies</t>
         </is>
       </c>
-      <c r="D84" s="2" t="n">
-        <v>45</v>
+      <c r="D84" t="n">
+        <v>108</v>
       </c>
       <c r="E84" t="n">
-        <v>6</v>
+        <v>10</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>BUN DONUT</t>
+        </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="H84" s="3" t="inlineStr">
-        <is>
-          <t>No catalogue photo yet.</t>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>DONET · RT-4 ( 12 GRM )</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>RAJ 100</t>
+          <t>RT-5</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Gift Box</t>
+          <t>Hair bun donut · 15 g</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3050,15 +3348,15 @@
           <t>Scrunchies</t>
         </is>
       </c>
-      <c r="D85" s="2" t="n">
-        <v>78</v>
+      <c r="D85" t="n">
+        <v>123</v>
       </c>
       <c r="E85" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>100 GIFT BOX</t>
+          <t>BUN DONUT</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -3066,12 +3364,21 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="H85" s="3" t="inlineStr"/>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>DONET · RT-5 ( 15 GRM )</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>RC-202</t>
+          <t>RT-6</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Hair bun donut · 18 g</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3079,15 +3386,15 @@
           <t>Scrunchies</t>
         </is>
       </c>
-      <c r="D86" s="2" t="n">
-        <v>156</v>
+      <c r="D86" t="n">
+        <v>141</v>
       </c>
       <c r="E86" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>BUN DONUT</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -3095,12 +3402,21 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="H86" s="3" t="inlineStr"/>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>DONET · RT-6 ( 18 GRM )</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>RC-254</t>
+          <t>RT-7</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Hair bun donut · 20 g</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3108,32 +3424,37 @@
           <t>Scrunchies</t>
         </is>
       </c>
-      <c r="D87" s="2" t="n">
-        <v>150</v>
+      <c r="D87" t="n">
+        <v>159</v>
       </c>
       <c r="E87" t="n">
-        <v>3</v>
+        <v>10</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>BUN DONUT</t>
+        </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="H87" s="3" t="inlineStr">
-        <is>
-          <t>No catalogue photo yet.</t>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>DONET · RT-7 ( 20 GRM )</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>RC-605</t>
+          <t>RT-8</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>36 pc · Rabit Fur</t>
+          <t>Hair bun donut · 22 g</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3141,15 +3462,15 @@
           <t>Scrunchies</t>
         </is>
       </c>
-      <c r="D88" s="2" t="n">
-        <v>84</v>
+      <c r="D88" t="n">
+        <v>183</v>
       </c>
       <c r="E88" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>RC-605</t>
+          <t>BUN DONUT</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -3157,21 +3478,21 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="H88" s="3" t="inlineStr">
-        <is>
-          <t>Rate 24 Oct 2026: ₹81 → ₹84.</t>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>DONET · RT-8 ( 22 GRM )</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>RC-610</t>
+          <t>RT-9</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Mobilon Rubber</t>
+          <t>Hair bun donut · 25 g</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3179,27 +3500,37 @@
           <t>Scrunchies</t>
         </is>
       </c>
-      <c r="D89" s="2" t="n">
-        <v>18</v>
+      <c r="D89" t="n">
+        <v>207</v>
       </c>
       <c r="E89" t="n">
         <v>10</v>
       </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>BUN DONUT</t>
+        </is>
+      </c>
       <c r="G89" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="H89" s="3" t="inlineStr">
-        <is>
-          <t>No catalogue photo yet.</t>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>DONET · RT-9 ( 25 GRM )</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>RC-611</t>
+          <t>RT-10</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Hair bun donut · 30 g</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3207,27 +3538,32 @@
           <t>Scrunchies</t>
         </is>
       </c>
-      <c r="D90" s="2" t="n">
-        <v>60</v>
+      <c r="D90" t="n">
+        <v>255</v>
       </c>
       <c r="E90" t="n">
-        <v>6</v>
+        <v>10</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>BUN DONUT</t>
+        </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="H90" s="3" t="inlineStr">
-        <is>
-          <t>No catalogue photo yet.</t>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>DONET · RT-10 ( 30 GM )</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>RC-612</t>
+          <t>XL-30 PC</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3235,99 +3571,93 @@
           <t>Scrunchies</t>
         </is>
       </c>
-      <c r="D91" s="2" t="n">
-        <v>72</v>
+      <c r="D91" t="n">
+        <v>27</v>
       </c>
       <c r="E91" t="n">
-        <v>6</v>
+        <v>10</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>XL / XXL 30 PC</t>
+        </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="H91" s="3" t="inlineStr">
-        <is>
-          <t>No catalogue photo yet.</t>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>UNIQUE MODEL</t>
         </is>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="4" t="inlineStr">
-        <is>
-          <t>RC-613</t>
-        </is>
-      </c>
-      <c r="B92" s="4" t="inlineStr">
-        <is>
-          <t>12 pc · Tier Rubed</t>
-        </is>
-      </c>
-      <c r="C92" s="4" t="inlineStr">
-        <is>
-          <t>Scrunchies</t>
-        </is>
-      </c>
-      <c r="D92" s="5" t="n">
-        <v>31.5</v>
-      </c>
-      <c r="E92" s="4" t="n">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>XXL-30 PC</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Scrunchies</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>33</v>
+      </c>
+      <c r="E92" t="n">
         <v>10</v>
       </c>
-      <c r="F92" s="4" t="inlineStr">
-        <is>
-          <t>T-613</t>
-        </is>
-      </c>
-      <c r="G92" s="4" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H92" s="6" t="inlineStr">
-        <is>
-          <t>Catalogue says T-613 – same item? Rate 24 Oct 2026: ₹30 → ₹31.5.</t>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>XL / XXL 30 PC</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>UNIQUE MODEL</t>
         </is>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="4" t="inlineStr">
-        <is>
-          <t>RC-614</t>
-        </is>
-      </c>
-      <c r="B93" s="4" t="inlineStr"/>
-      <c r="C93" s="4" t="inlineStr">
-        <is>
-          <t>Scrunchies</t>
-        </is>
-      </c>
-      <c r="D93" s="5" t="n">
-        <v>31.5</v>
-      </c>
-      <c r="E93" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="F93" s="4" t="inlineStr">
-        <is>
-          <t>T-614</t>
-        </is>
-      </c>
-      <c r="G93" s="4" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H93" s="6" t="inlineStr">
-        <is>
-          <t>Catalogue says T-614 – same item? Rate 24 Oct 2026: ₹30 → ₹31.5.</t>
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>1105</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Scrunchies</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>39</v>
+      </c>
+      <c r="E93" t="n">
+        <v>8</v>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>TRISHONA - 4</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>RC-615</t>
+          <t>1125</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3335,27 +3665,27 @@
           <t>Scrunchies</t>
         </is>
       </c>
-      <c r="D94" s="2" t="n">
-        <v>31.5</v>
+      <c r="D94" t="n">
+        <v>66</v>
       </c>
       <c r="E94" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="H94" s="3" t="inlineStr">
-        <is>
-          <t>No catalogue photo yet. Rate 24 Oct 2026: ₹30 → ₹31.5.</t>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>TRISHONA - 4</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>RC-616</t>
+          <t>340</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3363,27 +3693,27 @@
           <t>Scrunchies</t>
         </is>
       </c>
-      <c r="D95" s="2" t="n">
-        <v>60</v>
+      <c r="D95" t="n">
+        <v>51</v>
       </c>
       <c r="E95" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="H95" s="3" t="inlineStr">
-        <is>
-          <t>No catalogue photo yet.</t>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>TRISHONA - 4</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>RC-617</t>
+          <t>439</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3391,96 +3721,83 @@
           <t>Scrunchies</t>
         </is>
       </c>
-      <c r="D96" s="2" t="n">
-        <v>144</v>
+      <c r="D96" t="n">
+        <v>81</v>
       </c>
       <c r="E96" t="n">
+        <v>4</v>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>RAJ  I  WINDOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>845</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Scrunchies</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="E97" t="n">
         <v>6</v>
       </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>RC-617</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H96" s="3" t="inlineStr"/>
-    </row>
-    <row r="97">
-      <c r="A97" s="4" t="inlineStr">
-        <is>
-          <t>RC-618</t>
-        </is>
-      </c>
-      <c r="B97" s="4" t="inlineStr"/>
-      <c r="C97" s="4" t="inlineStr">
-        <is>
-          <t>Scrunchies</t>
-        </is>
-      </c>
-      <c r="D97" s="5" t="n">
-        <v>51</v>
-      </c>
-      <c r="E97" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="F97" s="4" t="inlineStr">
-        <is>
-          <t>T-618</t>
-        </is>
-      </c>
-      <c r="G97" s="4" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H97" s="6" t="inlineStr">
-        <is>
-          <t>Catalogue says T-618 – same item?</t>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>TRISHONA- 2</t>
         </is>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="4" t="inlineStr">
-        <is>
-          <t>RC-619</t>
-        </is>
-      </c>
-      <c r="B98" s="4" t="inlineStr"/>
-      <c r="C98" s="4" t="inlineStr">
-        <is>
-          <t>Scrunchies</t>
-        </is>
-      </c>
-      <c r="D98" s="5" t="n">
-        <v>36</v>
-      </c>
-      <c r="E98" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="F98" s="4" t="inlineStr">
-        <is>
-          <t>T-619</t>
-        </is>
-      </c>
-      <c r="G98" s="4" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H98" s="6" t="inlineStr">
-        <is>
-          <t>Catalogue says T-619 – same item?</t>
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>935</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Scrunchies</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>81</v>
+      </c>
+      <c r="E98" t="n">
+        <v>4</v>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>JUMBO BOX</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>RJ-1001</t>
+          <t>1111</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3488,32 +3805,27 @@
           <t>Scrunchies</t>
         </is>
       </c>
-      <c r="D99" s="2" t="n">
-        <v>96</v>
+      <c r="D99" t="n">
+        <v>36</v>
       </c>
       <c r="E99" t="n">
-        <v>5</v>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>1001</t>
-        </is>
+        <v>4</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="H99" s="3" t="inlineStr">
-        <is>
-          <t>Rate 24 Oct 2026: ₹90 → ₹96.</t>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>TOKYO</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>RJ-1002</t>
+          <t>RJ-1009</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3521,32 +3833,27 @@
           <t>Scrunchies</t>
         </is>
       </c>
-      <c r="D100" s="2" t="n">
-        <v>102</v>
+      <c r="D100" t="n">
+        <v>105</v>
       </c>
       <c r="E100" t="n">
-        <v>6</v>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>1002</t>
-        </is>
+        <v>2</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="H100" s="3" t="inlineStr">
-        <is>
-          <t>Rate 24 Oct 2026: ₹90 → ₹102.</t>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>1000-RAJ</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>RJ-1003</t>
+          <t>RT-616</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3554,48 +3861,43 @@
           <t>Scrunchies</t>
         </is>
       </c>
-      <c r="D101" s="2" t="n">
-        <v>108</v>
+      <c r="D101" t="n">
+        <v>63</v>
       </c>
       <c r="E101" t="n">
-        <v>6</v>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>1003</t>
-        </is>
+        <v>10</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="H101" s="3" t="inlineStr">
-        <is>
-          <t>Rate 24 Oct 2026: ₹96 → ₹108.</t>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>RT-600</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>RJ-1004</t>
+          <t>RC-258</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Scrunchies</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="n">
-        <v>54</v>
+          <t>Tie Bow</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>147</v>
       </c>
       <c r="E102" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>1004</t>
+          <t>RC 258</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -3603,121 +3905,131 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="H102" s="3" t="inlineStr">
-        <is>
-          <t>Rate 24 Oct 2026: ₹51 → ₹54.</t>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>TIE BOW (LOOSE)</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>RJ-1005</t>
+          <t>RC-259</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Scrunchies</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="n">
-        <v>120</v>
+          <t>Tie Bow</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>147</v>
       </c>
       <c r="E103" t="n">
-        <v>6</v>
+        <v>3</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>RC 259</t>
+        </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="H103" s="3" t="inlineStr">
-        <is>
-          <t>No catalogue photo yet. Rate 24 Oct 2026: ₹108 → ₹120.</t>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>TIE BOW (LOOSE)</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>RJ-1006</t>
+          <t>RC-278</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Scrunchies</t>
-        </is>
-      </c>
-      <c r="D104" s="2" t="n">
-        <v>78</v>
+          <t>Tie Bow</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>81</v>
       </c>
       <c r="E104" t="n">
         <v>6</v>
       </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>RC 278</t>
+        </is>
+      </c>
       <c r="G104" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="H104" s="3" t="inlineStr">
-        <is>
-          <t>No catalogue photo yet. Rate 24 Oct 2026: ₹72 → ₹78.</t>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>TIE BOW (LOOSE)</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>RJ-1007</t>
+          <t>RC-267</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Scrunchies</t>
-        </is>
-      </c>
-      <c r="D105" s="2" t="n">
-        <v>108</v>
+          <t>Tie Bow</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>141</v>
       </c>
       <c r="E105" t="n">
         <v>3</v>
       </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>RC 267</t>
+        </is>
+      </c>
       <c r="G105" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="H105" s="3" t="inlineStr">
-        <is>
-          <t>No catalogue photo yet. Rate 24 Oct 2026: ₹102 → ₹108.</t>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>TIE BOW (LOOSE)</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>RT-1</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>Hair bun donut · 8 g</t>
+          <t>RC-274</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Scrunchies</t>
-        </is>
-      </c>
-      <c r="D106" s="2" t="n">
-        <v>78</v>
+          <t>Tie Bow</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>123</v>
       </c>
       <c r="E106" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>BUN DONUT</t>
+          <t>RC 274</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -3725,37 +4037,32 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="H106" s="3" t="inlineStr">
-        <is>
-          <t>Rate 24 Oct 2026: ₹81 → ₹78.</t>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>TIE BOW (LOOSE)</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>RT-10</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>Hair bun donut · 30 g</t>
+          <t>RC-275</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Scrunchies</t>
-        </is>
-      </c>
-      <c r="D107" s="2" t="n">
-        <v>252</v>
+          <t>Tie Bow</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>135</v>
       </c>
       <c r="E107" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>BUN DONUT</t>
+          <t>RC 275</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -3763,33 +4070,32 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="H107" s="3" t="inlineStr"/>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>TIE BOW (LOOSE)</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>RT-2</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>Hair bun donut · 10 g</t>
+          <t>RC-503</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Scrunchies</t>
-        </is>
-      </c>
-      <c r="D108" s="2" t="n">
-        <v>87</v>
+          <t>Tie Bow</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>93</v>
       </c>
       <c r="E108" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>BUN DONUT</t>
+          <t>RC 503</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -3797,37 +4103,32 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="H108" s="3" t="inlineStr">
-        <is>
-          <t>Rate 24 Oct 2026: ₹90 → ₹87.</t>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>TIE BOW SMALL (LONG BOX)</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>RT-3</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>Hair bun donut · 12 g</t>
+          <t>RC-504</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Scrunchies</t>
-        </is>
-      </c>
-      <c r="D109" s="2" t="n">
-        <v>105</v>
+          <t>Tie Bow</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>93</v>
       </c>
       <c r="E109" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>BUN DONUT</t>
+          <t>RC 504</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -3835,37 +4136,32 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="H109" s="3" t="inlineStr">
-        <is>
-          <t>Rate 24 Oct 2026: ₹108 → ₹105.</t>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>TIE BOW SMALL (LONG BOX)</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>RT-4</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>Hair bun donut · 15 g</t>
+          <t>RC-256</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Scrunchies</t>
-        </is>
-      </c>
-      <c r="D110" s="2" t="n">
-        <v>120</v>
+          <t>Tie Bow</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>111</v>
       </c>
       <c r="E110" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>BUN DONUT</t>
+          <t>RC 256</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -3873,37 +4169,32 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="H110" s="3" t="inlineStr">
-        <is>
-          <t>Rate 24 Oct 2026: ₹126 → ₹120.</t>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>TIE BOW (LOOSE)</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>RT-5</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>Hair bun donut · 18 g</t>
+          <t>RC-266</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Scrunchies</t>
-        </is>
-      </c>
-      <c r="D111" s="2" t="n">
-        <v>138</v>
+          <t>Tie Bow</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>75</v>
       </c>
       <c r="E111" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>BUN DONUT</t>
+          <t>RC 266</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -3911,37 +4202,32 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="H111" s="3" t="inlineStr">
-        <is>
-          <t>Rate 24 Oct 2026: ₹150 → ₹138.</t>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>TIE BOW (LOOSE)</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>RT-6</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>Hair bun donut · 20 g</t>
+          <t>RC-262</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Scrunchies</t>
-        </is>
-      </c>
-      <c r="D112" s="2" t="n">
-        <v>156</v>
+          <t>Tie Bow</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>81</v>
       </c>
       <c r="E112" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>BUN DONUT</t>
+          <t>RC 262</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -3949,108 +4235,103 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="H112" s="3" t="inlineStr">
-        <is>
-          <t>Rate 24 Oct 2026: ₹180 → ₹156.</t>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>TIE BOW (LOOSE)</t>
         </is>
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="4" t="inlineStr">
-        <is>
-          <t>RT-601</t>
-        </is>
-      </c>
-      <c r="B113" s="4" t="inlineStr">
-        <is>
-          <t>Tier Rubed</t>
-        </is>
-      </c>
-      <c r="C113" s="4" t="inlineStr">
-        <is>
-          <t>Scrunchies</t>
-        </is>
-      </c>
-      <c r="D113" s="5" t="n">
-        <v>75</v>
-      </c>
-      <c r="E113" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="F113" s="4" t="inlineStr">
-        <is>
-          <t>RC-601</t>
-        </is>
-      </c>
-      <c r="G113" s="4" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H113" s="6" t="inlineStr">
-        <is>
-          <t>Catalogue says RC-601, rate list says RT-601 – same item?</t>
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>RC-255</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Tie Bow</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>81</v>
+      </c>
+      <c r="E113" t="n">
+        <v>3</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>RC 255</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>TIE BOW (LOOSE)</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>RT-602</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>Tier Rubed</t>
+          <t>RC-264</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Scrunchies</t>
-        </is>
-      </c>
-      <c r="D114" s="2" t="n">
-        <v>75</v>
+          <t>Tie Bow</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>147</v>
       </c>
       <c r="E114" t="n">
-        <v>6</v>
+        <v>3</v>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>RC 264</t>
+        </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="H114" s="3" t="inlineStr">
-        <is>
-          <t>No catalogue photo yet.</t>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>TIE BOW (LOOSE)</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>RT-7</t>
+          <t>RC-252</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Hair bun donut · 22 g</t>
+          <t>Rambow Tie Bow</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Scrunchies</t>
-        </is>
-      </c>
-      <c r="D115" s="2" t="n">
-        <v>180</v>
+          <t>Tie Bow</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>141</v>
       </c>
       <c r="E115" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>BUN DONUT</t>
+          <t>RC 252</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -4058,761 +4339,37 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="H115" s="3" t="inlineStr">
-        <is>
-          <t>Rate 24 Oct 2026: ₹198 → ₹180.</t>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>TIE BOW (LOOSE) · RC-252 RAMBOW TIE BOW</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>RT-8</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>Hair bun donut · 25 g</t>
+          <t>CARTOON</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Scrunchies</t>
-        </is>
-      </c>
-      <c r="D116" s="2" t="n">
-        <v>204</v>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>403</v>
       </c>
       <c r="E116" t="n">
-        <v>10</v>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>BUN DONUT</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H116" s="3" t="inlineStr">
-        <is>
-          <t>Rate 24 Oct 2026: ₹220 → ₹204.</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>SUMO-RINKLE</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>Scrunchies</t>
-        </is>
-      </c>
-      <c r="D117" s="2" t="n">
-        <v>114</v>
-      </c>
-      <c r="E117" t="n">
-        <v>4</v>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>SUMO RINKLE</t>
-        </is>
-      </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H117" s="3" t="inlineStr"/>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>TIER RUBED</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>Scrunchies</t>
-        </is>
-      </c>
-      <c r="D118" s="2" t="n">
-        <v>36</v>
-      </c>
-      <c r="E118" t="n">
-        <v>10</v>
-      </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H118" s="3" t="inlineStr">
-        <is>
-          <t>No catalogue photo yet.</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>XL 30 PC</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>Scrunchies</t>
-        </is>
-      </c>
-      <c r="D119" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="E119" t="n">
-        <v>10</v>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>XL / XXL 30 PC</t>
-        </is>
-      </c>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H119" s="3" t="inlineStr"/>
-    </row>
-    <row r="120">
-      <c r="A120" s="4" t="inlineStr">
-        <is>
-          <t>XL 72 PC</t>
-        </is>
-      </c>
-      <c r="B120" s="4" t="inlineStr"/>
-      <c r="C120" s="4" t="inlineStr">
-        <is>
-          <t>Scrunchies</t>
-        </is>
-      </c>
-      <c r="D120" s="5" t="n">
-        <v>48</v>
-      </c>
-      <c r="E120" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="F120" s="4" t="inlineStr"/>
-      <c r="G120" s="4" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H120" s="6" t="inlineStr">
-        <is>
-          <t>Same as 'XL (72 PC RUBED)'? Same rate and packet – delete one row.</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>XL 72 PC RUBED</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>Scrunchies</t>
-        </is>
-      </c>
-      <c r="D121" s="2" t="n">
-        <v>48</v>
-      </c>
-      <c r="E121" t="n">
-        <v>6</v>
-      </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H121" s="3" t="inlineStr">
-        <is>
-          <t>No catalogue photo yet.</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>XXL 30 PC</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>Scrunchies</t>
-        </is>
-      </c>
-      <c r="D122" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="E122" t="n">
-        <v>10</v>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>XL / XXL 30 PC</t>
-        </is>
-      </c>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H122" s="3" t="inlineStr">
-        <is>
-          <t>Rate 24 Oct 2026: ₹28.5 → ₹30.</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>XXL 72 PC RUBED</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>Scrunchies</t>
-        </is>
-      </c>
-      <c r="D123" s="2" t="n">
-        <v>63</v>
-      </c>
-      <c r="E123" t="n">
-        <v>6</v>
-      </c>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H123" s="3" t="inlineStr">
-        <is>
-          <t>No catalogue photo yet. Rate 24 Oct 2026: ₹60 → ₹63.</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>278</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>Tie Bow</t>
-        </is>
-      </c>
-      <c r="D124" s="2" t="n">
-        <v>78</v>
-      </c>
-      <c r="E124" t="n">
-        <v>6</v>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>RC 278</t>
-        </is>
-      </c>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H124" s="3" t="inlineStr"/>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>503</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>Tie Bow</t>
-        </is>
-      </c>
-      <c r="D125" s="2" t="n">
-        <v>90</v>
-      </c>
-      <c r="E125" t="n">
-        <v>4</v>
-      </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>RC 503</t>
-        </is>
-      </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H125" s="3" t="inlineStr"/>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>RC-252</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>Rambow Tie Bow</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>Tie Bow</t>
-        </is>
-      </c>
-      <c r="D126" s="2" t="n">
-        <v>138</v>
-      </c>
-      <c r="E126" t="n">
-        <v>3</v>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>RC 252</t>
-        </is>
-      </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H126" s="3" t="inlineStr"/>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>RC-253</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>Tie Bow</t>
-        </is>
-      </c>
-      <c r="D127" s="2" t="n">
-        <v>138</v>
-      </c>
-      <c r="E127" t="n">
-        <v>3</v>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>RC 253</t>
-        </is>
-      </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H127" s="3" t="inlineStr"/>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>RC-255</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>Tie Bow</t>
-        </is>
-      </c>
-      <c r="D128" s="2" t="n">
-        <v>78</v>
-      </c>
-      <c r="E128" t="n">
-        <v>3</v>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>RC 255</t>
-        </is>
-      </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H128" s="3" t="inlineStr"/>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>RC-256</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>Tie Bow</t>
-        </is>
-      </c>
-      <c r="D129" s="2" t="n">
-        <v>108</v>
-      </c>
-      <c r="E129" t="n">
-        <v>4</v>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>RC 256</t>
-        </is>
-      </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H129" s="3" t="inlineStr"/>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>RC-258</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>Tie Bow</t>
-        </is>
-      </c>
-      <c r="D130" s="2" t="n">
-        <v>144</v>
-      </c>
-      <c r="E130" t="n">
-        <v>3</v>
-      </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>RC 258</t>
-        </is>
-      </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H130" s="3" t="inlineStr"/>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>RC-259</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>Tie Bow</t>
-        </is>
-      </c>
-      <c r="D131" s="2" t="n">
-        <v>144</v>
-      </c>
-      <c r="E131" t="n">
-        <v>3</v>
-      </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>RC 259</t>
-        </is>
-      </c>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H131" s="3" t="inlineStr"/>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>RC-264</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>Tie Bow</t>
-        </is>
-      </c>
-      <c r="D132" s="2" t="n">
-        <v>144</v>
-      </c>
-      <c r="E132" t="n">
-        <v>3</v>
-      </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>RC 264</t>
-        </is>
-      </c>
-      <c r="G132" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H132" s="3" t="inlineStr"/>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>RC-265</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>Tie Bow</t>
-        </is>
-      </c>
-      <c r="D133" s="2" t="n">
-        <v>150</v>
-      </c>
-      <c r="E133" t="n">
-        <v>3</v>
-      </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>RC 265</t>
-        </is>
-      </c>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H133" s="3" t="inlineStr"/>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>RC-266</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>Tie Bow</t>
-        </is>
-      </c>
-      <c r="D134" s="2" t="n">
-        <v>72</v>
-      </c>
-      <c r="E134" t="n">
-        <v>6</v>
-      </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>RC 266</t>
-        </is>
-      </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H134" s="3" t="inlineStr"/>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>RC-267</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>Tie Bow</t>
-        </is>
-      </c>
-      <c r="D135" s="2" t="n">
-        <v>138</v>
-      </c>
-      <c r="E135" t="n">
-        <v>3</v>
-      </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>RC 267</t>
-        </is>
-      </c>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H135" s="3" t="inlineStr"/>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>RC-274</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>Tie Bow</t>
-        </is>
-      </c>
-      <c r="D136" s="2" t="n">
-        <v>120</v>
-      </c>
-      <c r="E136" t="n">
-        <v>3</v>
-      </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>RC 274</t>
-        </is>
-      </c>
-      <c r="G136" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H136" s="3" t="inlineStr"/>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>RC-275</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>Tie Bow</t>
-        </is>
-      </c>
-      <c r="D137" s="2" t="n">
-        <v>132</v>
-      </c>
-      <c r="E137" t="n">
-        <v>3</v>
-      </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>RC 275</t>
-        </is>
-      </c>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H137" s="3" t="inlineStr"/>
-    </row>
-    <row r="138">
-      <c r="A138" s="4" t="inlineStr">
-        <is>
-          <t>RC-504</t>
-        </is>
-      </c>
-      <c r="B138" s="4" t="inlineStr"/>
-      <c r="C138" s="4" t="inlineStr">
-        <is>
-          <t>Tie Bow</t>
-        </is>
-      </c>
-      <c r="D138" s="5" t="n">
-        <v>90</v>
-      </c>
-      <c r="E138" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="F138" s="4" t="inlineStr">
-        <is>
-          <t>RC 504</t>
-        </is>
-      </c>
-      <c r="G138" s="4" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H138" s="6" t="inlineStr">
-        <is>
-          <t>Old rate list had this under SCRUNCHIES; catalogue has it under tie bows – moved to Tie Bow.</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" s="4" t="inlineStr">
-        <is>
-          <t>RC-511</t>
-        </is>
-      </c>
-      <c r="B139" s="4" t="inlineStr"/>
-      <c r="C139" s="4" t="inlineStr">
-        <is>
-          <t>Tie Bow</t>
-        </is>
-      </c>
-      <c r="D139" s="5" t="n">
-        <v>96</v>
-      </c>
-      <c r="E139" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="F139" s="4" t="inlineStr">
-        <is>
-          <t>RC 511</t>
-        </is>
-      </c>
-      <c r="G139" s="4" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H139" s="6" t="inlineStr">
-        <is>
-          <t>Rate list also has a scrunchies item '511' at ₹33 – different item?</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" s="4" t="inlineStr">
-        <is>
-          <t>CARTOON</t>
-        </is>
-      </c>
-      <c r="B140" s="4" t="inlineStr"/>
-      <c r="C140" s="4" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="D140" s="5" t="n">
-        <v>400</v>
-      </c>
-      <c r="E140" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F140" s="4" t="inlineStr"/>
-      <c r="G140" s="4" t="inlineStr">
-        <is>
           <t>N</t>
         </is>
       </c>
-      <c r="H140" s="6" t="inlineStr">
-        <is>
-          <t>Carton charge, not a product. Keep hidden (or tell us if it should be added to orders).</t>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Carton charge, not a product. Keep hidden.</t>
         </is>
       </c>
     </row>
@@ -4840,7 +4397,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -4897,7 +4453,6 @@
         </is>
       </c>
     </row>
-    <row r="11"/>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>

--- a/website/Website Rates (for Google Sheet).xlsx
+++ b/website/Website Rates (for Google Sheet).xlsx
@@ -448,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H116"/>
+  <dimension ref="A1:H124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4348,26 +4348,285 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>CARTOON</t>
+          <t>TESLA-710</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Clutchers</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>403</v>
+        <v>126</v>
       </c>
       <c r="E116" t="n">
         <v>1</v>
       </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>TESLA 710</t>
+        </is>
+      </c>
       <c r="G116" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Rate given by Raj, 29 Oct 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>986</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Scrunchies</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>86</v>
+      </c>
+      <c r="E117" t="n">
+        <v>6</v>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>986</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Rate given by Raj, 29 Oct 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>991</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Scrunchies</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>104</v>
+      </c>
+      <c r="E118" t="n">
+        <v>4</v>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>991</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Rate given by Raj, 29 Oct 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>36 PC NYLON RUBBER</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Scrunchies</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>26</v>
+      </c>
+      <c r="E119" t="n">
+        <v>6</v>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>36 PC NYLON RUBBER</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Rate given by Raj, 29 Oct 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>1126</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Scrunchies</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>92</v>
+      </c>
+      <c r="E120" t="n">
+        <v>4</v>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Rate given by Raj, 29 Oct 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>RC-253</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Tie Bow</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>140</v>
+      </c>
+      <c r="E121" t="n">
+        <v>3</v>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>RC 253</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Rate given by Raj, 29 Oct 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>RC-511</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Tie Bow</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>96</v>
+      </c>
+      <c r="E122" t="n">
+        <v>4</v>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>RC 511</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Rate given by Raj, 29 Oct 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>RC-265</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Tie Bow</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>150</v>
+      </c>
+      <c r="E123" t="n">
+        <v>3</v>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>RC 265</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Rate given by Raj, 29 Oct 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>CARTOON</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>403</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1</v>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
           <t>N</t>
         </is>
       </c>
-      <c r="H116" t="inlineStr">
+      <c r="H124" t="inlineStr">
         <is>
           <t>Carton charge, not a product. Keep hidden.</t>
         </is>
